--- a/KSBC_Loans_Portfolio_Master.xlsx
+++ b/KSBC_Loans_Portfolio_Master.xlsx
@@ -462,55 +462,55 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c0000041-1111-4111-c111-111111111111</v>
+        <v>c0000043-1111-4111-c111-111111111111</v>
       </c>
       <c r="B2" t="str">
-        <v>b0000041-1111-4111-b111-111111111111</v>
+        <v>b0000043-1111-4111-b111-111111111111</v>
       </c>
       <c r="C2" t="str">
-        <v>Alexander Chen</v>
+        <v>David Reddy</v>
       </c>
       <c r="D2" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E2" t="str">
-        <v>KSBC-SAV-10061172</v>
+        <v>KSBC-SAV-10064156</v>
       </c>
       <c r="F2">
-        <v>7600000</v>
+        <v>8560000</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I2" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J2" t="str">
-        <v>DISBURSED</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K2">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L2" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M2" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N2" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
+        <v>Standard low-risk profile approved under baseline AI parameters.</v>
       </c>
       <c r="O2" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P2" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q2" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R2" t="str">
         <v>2026-07-29T15:27:02.912599+00:00</v>
@@ -518,37 +518,37 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c0000049-1111-4111-c111-111111111111</v>
+        <v>c0000054-1111-4111-c111-111111111111</v>
       </c>
       <c r="B3" t="str">
-        <v>b0000049-1111-4111-b111-111111111111</v>
+        <v>b0000054-1111-4111-b111-111111111111</v>
       </c>
       <c r="C3" t="str">
-        <v>Ananya Taylor</v>
+        <v>Christopher Jenkins</v>
       </c>
       <c r="D3" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E3" t="str">
-        <v>KSBC-SAV-10073108</v>
+        <v>KSBC-SAV-10080568</v>
       </c>
       <c r="F3">
-        <v>11440000</v>
+        <v>1840000</v>
       </c>
       <c r="G3">
-        <v>4.5</v>
+        <v>8.25</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="I3" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J3" t="str">
-        <v>UNDERWRITING</v>
+        <v>REJECTED</v>
       </c>
       <c r="K3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L3" t="str">
         <v>LOW</v>
@@ -557,7 +557,7 @@
         <v>APPROVE</v>
       </c>
       <c r="N3" t="str">
-        <v>Standard low-risk profile approved under baseline AI parameters.</v>
+        <v>Gemini Risk Score: 36/100 (LOW) for Christopher Jenkins.</v>
       </c>
       <c r="O3" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -574,37 +574,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>c0000043-1111-4111-c111-111111111111</v>
+        <v>c0000053-1111-4111-c111-111111111111</v>
       </c>
       <c r="B4" t="str">
-        <v>b0000043-1111-4111-b111-111111111111</v>
+        <v>b0000053-1111-4111-b111-111111111111</v>
       </c>
       <c r="C4" t="str">
-        <v>David Reddy</v>
+        <v>Emily Lewis</v>
       </c>
       <c r="D4" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E4" t="str">
-        <v>KSBC-SAV-10064156</v>
+        <v>KSBC-SAV-10079076</v>
       </c>
       <c r="F4">
-        <v>8560000</v>
+        <v>1360000</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="I4" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J4" t="str">
-        <v>UNDERWRITING</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K4">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L4" t="str">
         <v>LOW</v>
@@ -613,16 +613,16 @@
         <v>APPROVE</v>
       </c>
       <c r="N4" t="str">
-        <v>Standard low-risk profile approved under baseline AI parameters.</v>
+        <v>Gemini Risk Score: 32/100 (LOW) for Emily Lewis.</v>
       </c>
       <c r="O4" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P4" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q4" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R4" t="str">
         <v>2026-07-29T15:27:02.912599+00:00</v>
@@ -630,46 +630,46 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>c0000054-1111-4111-c111-111111111111</v>
+        <v>c0000042-1111-4111-c111-111111111111</v>
       </c>
       <c r="B5" t="str">
-        <v>b0000054-1111-4111-b111-111111111111</v>
+        <v>b0000042-1111-4111-b111-111111111111</v>
       </c>
       <c r="C5" t="str">
-        <v>Christopher Jenkins</v>
+        <v>Sarah Green</v>
       </c>
       <c r="D5" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E5" t="str">
-        <v>KSBC-SAV-10080568</v>
+        <v>KSBC-SAV-10062664</v>
       </c>
       <c r="F5">
-        <v>1840000</v>
+        <v>8080000</v>
       </c>
       <c r="G5">
-        <v>8.25</v>
+        <v>5.25</v>
       </c>
       <c r="H5">
         <v>240</v>
       </c>
       <c r="I5" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J5" t="str">
         <v>REJECTED</v>
       </c>
       <c r="K5">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="L5" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M5" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N5" t="str">
-        <v>Gemini Risk Score: 36/100 (LOW) for Christopher Jenkins.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
       </c>
       <c r="O5" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -686,46 +686,46 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c0000053-1111-4111-c111-111111111111</v>
+        <v>c0000046-1111-4111-c111-111111111111</v>
       </c>
       <c r="B6" t="str">
-        <v>b0000053-1111-4111-b111-111111111111</v>
+        <v>b0000046-1111-4111-b111-111111111111</v>
       </c>
       <c r="C6" t="str">
-        <v>Emily Lewis</v>
+        <v>Rachel Davis</v>
       </c>
       <c r="D6" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E6" t="str">
-        <v>KSBC-SAV-10079076</v>
+        <v>KSBC-SAV-10068632</v>
       </c>
       <c r="F6">
-        <v>1360000</v>
+        <v>10000000</v>
       </c>
       <c r="G6">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="H6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I6" t="str">
         <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J6" t="str">
-        <v>DISBURSED</v>
+        <v>APPROVED</v>
       </c>
       <c r="K6">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="L6" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M6" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N6" t="str">
-        <v>Gemini Risk Score: 32/100 (LOW) for Emily Lewis.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
       </c>
       <c r="O6" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -734,7 +734,7 @@
         <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q6" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R6" t="str">
         <v>2026-07-29T15:27:02.912599+00:00</v>
@@ -742,52 +742,52 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c0000052-1111-4111-c111-111111111111</v>
+        <v>c0000044-1111-4111-c111-111111111111</v>
       </c>
       <c r="B7" t="str">
-        <v>b0000052-1111-4111-b111-111111111111</v>
+        <v>b0000044-1111-4111-b111-111111111111</v>
       </c>
       <c r="C7" t="str">
-        <v>Jessica Sanchez</v>
+        <v>Elena Smith</v>
       </c>
       <c r="D7" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E7" t="str">
-        <v>KSBC-SAV-10077584</v>
+        <v>KSBC-SAV-10065648</v>
       </c>
       <c r="F7">
-        <v>880000</v>
+        <v>9040000</v>
       </c>
       <c r="G7">
         <v>6.75</v>
       </c>
       <c r="H7">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="I7" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J7" t="str">
-        <v>APPROVED</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K7">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="L7" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M7" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N7" t="str">
-        <v>Gemini Risk Score: 28/100 (LOW) for Jessica Sanchez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
       </c>
       <c r="O7" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P7" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q7" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -798,46 +798,46 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>c0000051-1111-4111-c111-111111111111</v>
+        <v>c0000050-1111-4111-c111-111111111111</v>
       </c>
       <c r="B8" t="str">
-        <v>b0000051-1111-4111-b111-111111111111</v>
+        <v>b0000050-1111-4111-b111-111111111111</v>
       </c>
       <c r="C8" t="str">
-        <v>Michael Thompson</v>
+        <v>Rohan Martin</v>
       </c>
       <c r="D8" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E8" t="str">
-        <v>KSBC-SAV-10076092</v>
+        <v>KSBC-SAV-10074600</v>
       </c>
       <c r="F8">
-        <v>400000</v>
+        <v>11920000</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I8" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J8" t="str">
-        <v>UNDERWRITING</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L8" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M8" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N8" t="str">
-        <v>Gemini Risk Score: 24/100 (LOW) for Michael Thompson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rohan Martin.</v>
       </c>
       <c r="O8" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -854,34 +854,34 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>c0000050-1111-4111-c111-111111111111</v>
+        <v>c0000048-1111-4111-c111-111111111111</v>
       </c>
       <c r="B9" t="str">
-        <v>b0000050-1111-4111-b111-111111111111</v>
+        <v>b0000048-1111-4111-b111-111111111111</v>
       </c>
       <c r="C9" t="str">
-        <v>Rohan Martin</v>
+        <v>Priya Wilson</v>
       </c>
       <c r="D9" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E9" t="str">
-        <v>KSBC-SAV-10074600</v>
+        <v>KSBC-SAV-10071616</v>
       </c>
       <c r="F9">
-        <v>11920000</v>
+        <v>10960000</v>
       </c>
       <c r="G9">
-        <v>5.25</v>
+        <v>9.75</v>
       </c>
       <c r="H9">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="I9" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J9" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>REJECTED</v>
       </c>
       <c r="K9">
         <v>94</v>
@@ -893,7 +893,7 @@
         <v>REJECT</v>
       </c>
       <c r="N9" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rohan Martin.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
       </c>
       <c r="O9" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -910,34 +910,34 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>c0000048-1111-4111-c111-111111111111</v>
+        <v>c0000045-1111-4111-c111-111111111111</v>
       </c>
       <c r="B10" t="str">
-        <v>b0000048-1111-4111-b111-111111111111</v>
+        <v>b0000045-1111-4111-b111-111111111111</v>
       </c>
       <c r="C10" t="str">
-        <v>Priya Wilson</v>
+        <v>Marcus Jones</v>
       </c>
       <c r="D10" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E10" t="str">
-        <v>KSBC-SAV-10071616</v>
+        <v>KSBC-SAV-10067140</v>
       </c>
       <c r="F10">
-        <v>10960000</v>
+        <v>9520000</v>
       </c>
       <c r="G10">
-        <v>9.75</v>
+        <v>7.5</v>
       </c>
       <c r="H10">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="I10" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J10" t="str">
-        <v>REJECTED</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K10">
         <v>94</v>
@@ -949,7 +949,7 @@
         <v>REJECT</v>
       </c>
       <c r="N10" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
       </c>
       <c r="O10" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -966,46 +966,46 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>c0000047-1111-4111-c111-111111111111</v>
+        <v>c0000052-1111-4111-c111-111111111111</v>
       </c>
       <c r="B11" t="str">
-        <v>b0000047-1111-4111-b111-111111111111</v>
+        <v>b0000052-1111-4111-b111-111111111111</v>
       </c>
       <c r="C11" t="str">
-        <v>Vikram Hernandez</v>
+        <v>Jessica Sanchez</v>
       </c>
       <c r="D11" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E11" t="str">
-        <v>KSBC-SAV-10070124</v>
+        <v>KSBC-SAV-10077584</v>
       </c>
       <c r="F11">
-        <v>10480000</v>
+        <v>880000</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="H11">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I11" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J11" t="str">
-        <v>DISBURSED</v>
+        <v>APPROVED</v>
       </c>
       <c r="K11">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="L11" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M11" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N11" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Vikram Hernandez.</v>
+        <v>Gemini Risk Score: 28/100 (LOW) for Jessica Sanchez.</v>
       </c>
       <c r="O11" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1014,7 +1014,7 @@
         <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q11" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R11" t="str">
         <v>2026-07-29T15:27:02.912599+00:00</v>
@@ -1022,52 +1022,52 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>c0000046-1111-4111-c111-111111111111</v>
+        <v>c0000051-1111-4111-c111-111111111111</v>
       </c>
       <c r="B12" t="str">
-        <v>b0000046-1111-4111-b111-111111111111</v>
+        <v>b0000051-1111-4111-b111-111111111111</v>
       </c>
       <c r="C12" t="str">
-        <v>Rachel Davis</v>
+        <v>Michael Thompson</v>
       </c>
       <c r="D12" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E12" t="str">
-        <v>KSBC-SAV-10068632</v>
+        <v>KSBC-SAV-10076092</v>
       </c>
       <c r="F12">
-        <v>10000000</v>
+        <v>400000</v>
       </c>
       <c r="G12">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="H12">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="I12" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J12" t="str">
-        <v>APPROVED</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K12">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="L12" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M12" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N12" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
+        <v>Gemini Risk Score: 24/100 (LOW) for Michael Thompson.</v>
       </c>
       <c r="O12" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P12" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q12" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -1078,46 +1078,46 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>c0000045-1111-4111-c111-111111111111</v>
+        <v>c0000049-1111-4111-c111-111111111111</v>
       </c>
       <c r="B13" t="str">
-        <v>b0000045-1111-4111-b111-111111111111</v>
+        <v>b0000049-1111-4111-b111-111111111111</v>
       </c>
       <c r="C13" t="str">
-        <v>Marcus Jones</v>
+        <v>Ananya Taylor</v>
       </c>
       <c r="D13" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E13" t="str">
-        <v>KSBC-SAV-10067140</v>
+        <v>KSBC-SAV-10073108</v>
       </c>
       <c r="F13">
-        <v>9520000</v>
+        <v>11440000</v>
       </c>
       <c r="G13">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H13">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I13" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J13" t="str">
         <v>UNDERWRITING</v>
       </c>
       <c r="K13">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L13" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M13" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N13" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
+        <v>Standard low-risk profile approved under baseline AI parameters.</v>
       </c>
       <c r="O13" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1134,34 +1134,34 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>c0000044-1111-4111-c111-111111111111</v>
+        <v>c0000041-1111-4111-c111-111111111111</v>
       </c>
       <c r="B14" t="str">
-        <v>b0000044-1111-4111-b111-111111111111</v>
+        <v>b0000041-1111-4111-b111-111111111111</v>
       </c>
       <c r="C14" t="str">
-        <v>Elena Smith</v>
+        <v>Alexander Chen</v>
       </c>
       <c r="D14" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E14" t="str">
-        <v>KSBC-SAV-10065648</v>
+        <v>KSBC-SAV-10061172</v>
       </c>
       <c r="F14">
-        <v>9040000</v>
+        <v>7600000</v>
       </c>
       <c r="G14">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="H14">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="I14" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J14" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K14">
         <v>94</v>
@@ -1173,16 +1173,16 @@
         <v>REJECT</v>
       </c>
       <c r="N14" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
       </c>
       <c r="O14" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P14" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q14" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R14" t="str">
         <v>2026-07-29T15:27:02.912599+00:00</v>
@@ -1190,34 +1190,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>c0000042-1111-4111-c111-111111111111</v>
+        <v>c0000047-1111-4111-c111-111111111111</v>
       </c>
       <c r="B15" t="str">
-        <v>b0000042-1111-4111-b111-111111111111</v>
+        <v>b0000047-1111-4111-b111-111111111111</v>
       </c>
       <c r="C15" t="str">
-        <v>Sarah Green</v>
+        <v>Vikram Hernandez</v>
       </c>
       <c r="D15" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E15" t="str">
-        <v>KSBC-SAV-10062664</v>
+        <v>KSBC-SAV-10070124</v>
       </c>
       <c r="F15">
-        <v>8080000</v>
+        <v>10480000</v>
       </c>
       <c r="G15">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="H15">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="I15" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J15" t="str">
-        <v>REJECTED</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K15">
         <v>94</v>
@@ -1229,16 +1229,16 @@
         <v>REJECT</v>
       </c>
       <c r="N15" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Vikram Hernandez.</v>
       </c>
       <c r="O15" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P15" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q15" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R15" t="str">
         <v>2026-07-29T15:27:02.912599+00:00</v>
@@ -1246,37 +1246,37 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>c0000034-1111-4111-c111-111111111111</v>
+        <v>c0000024-1111-4111-c111-111111111111</v>
       </c>
       <c r="B16" t="str">
-        <v>b0000034-1111-4111-b111-111111111111</v>
+        <v>b0000024-1111-4111-b111-111111111111</v>
       </c>
       <c r="C16" t="str">
-        <v>Jack Lopez</v>
+        <v>Benjamin Perez</v>
       </c>
       <c r="D16" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E16" t="str">
-        <v>KSBC-SAV-10050728</v>
+        <v>KSBC-SAV-10035808</v>
       </c>
       <c r="F16">
-        <v>4240000</v>
+        <v>11440000</v>
       </c>
       <c r="G16">
-        <v>5.25</v>
+        <v>9.75</v>
       </c>
       <c r="H16">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="I16" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J16" t="str">
-        <v>APPROVED</v>
+        <v>REJECTED</v>
       </c>
       <c r="K16">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L16" t="str">
         <v>HIGH</v>
@@ -1285,13 +1285,13 @@
         <v>REJECT</v>
       </c>
       <c r="N16" t="str">
-        <v>Gemini Risk Score: 78/100 (HIGH) for Jack Lopez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Benjamin Perez.</v>
       </c>
       <c r="O16" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P16" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q16" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -1358,55 +1358,55 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>c0000023-1111-4111-c111-111111111111</v>
+        <v>c0000031-1111-4111-c111-111111111111</v>
       </c>
       <c r="B18" t="str">
-        <v>b0000023-1111-4111-b111-111111111111</v>
+        <v>b0000031-1111-4111-b111-111111111111</v>
       </c>
       <c r="C18" t="str">
-        <v>Ava Jackson</v>
+        <v>Harper Williams</v>
       </c>
       <c r="D18" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E18" t="str">
-        <v>KSBC-SAV-10034316</v>
+        <v>KSBC-SAV-10046252</v>
       </c>
       <c r="F18">
-        <v>10960000</v>
+        <v>2800000</v>
       </c>
       <c r="G18">
         <v>9</v>
       </c>
       <c r="H18">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I18" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J18" t="str">
-        <v>DISBURSED</v>
+        <v>DRAFT</v>
       </c>
       <c r="K18">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="L18" t="str">
-        <v>HIGH</v>
+        <v>MODERATE</v>
       </c>
       <c r="M18" t="str">
-        <v>REJECT</v>
+        <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N18" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ava Jackson.</v>
+        <v>Gemini Risk Score: 62/100 (MODERATE) for Harper Williams.</v>
       </c>
       <c r="O18" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P18" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q18" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R18" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -1414,46 +1414,46 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>c0000024-1111-4111-c111-111111111111</v>
+        <v>c0000032-1111-4111-c111-111111111111</v>
       </c>
       <c r="B19" t="str">
-        <v>b0000024-1111-4111-b111-111111111111</v>
+        <v>b0000032-1111-4111-b111-111111111111</v>
       </c>
       <c r="C19" t="str">
-        <v>Benjamin Perez</v>
+        <v>Sebastian Garcia</v>
       </c>
       <c r="D19" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E19" t="str">
-        <v>KSBC-SAV-10035808</v>
+        <v>KSBC-SAV-10047744</v>
       </c>
       <c r="F19">
-        <v>11440000</v>
+        <v>3280000</v>
       </c>
       <c r="G19">
         <v>9.75</v>
       </c>
       <c r="H19">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="I19" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J19" t="str">
-        <v>REJECTED</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K19">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="L19" t="str">
-        <v>HIGH</v>
+        <v>MODERATE</v>
       </c>
       <c r="M19" t="str">
-        <v>REJECT</v>
+        <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N19" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Benjamin Perez.</v>
+        <v>Gemini Risk Score: 68/100 (MODERATE) for Sebastian Garcia.</v>
       </c>
       <c r="O19" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1470,37 +1470,37 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>c0000025-1111-4111-c111-111111111111</v>
+        <v>c0000033-1111-4111-c111-111111111111</v>
       </c>
       <c r="B20" t="str">
-        <v>b0000025-1111-4111-b111-111111111111</v>
+        <v>b0000033-1111-4111-b111-111111111111</v>
       </c>
       <c r="C20" t="str">
-        <v>Mia Harris</v>
+        <v>Evelyn Rodriguez</v>
       </c>
       <c r="D20" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E20" t="str">
-        <v>KSBC-SAV-10037300</v>
+        <v>KSBC-SAV-10049236</v>
       </c>
       <c r="F20">
-        <v>11920000</v>
+        <v>3760000</v>
       </c>
       <c r="G20">
         <v>4.5</v>
       </c>
       <c r="H20">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I20" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J20" t="str">
-        <v>DRAFT</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K20">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L20" t="str">
         <v>HIGH</v>
@@ -1509,7 +1509,7 @@
         <v>REJECT</v>
       </c>
       <c r="N20" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Mia Harris.</v>
+        <v>Gemini Risk Score: 73/100 (HIGH) for Evelyn Rodriguez.</v>
       </c>
       <c r="O20" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1526,55 +1526,55 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>c0000026-1111-4111-c111-111111111111</v>
+        <v>c0000035-1111-4111-c111-111111111111</v>
       </c>
       <c r="B21" t="str">
-        <v>b0000026-1111-4111-b111-111111111111</v>
+        <v>b0000035-1111-4111-b111-111111111111</v>
       </c>
       <c r="C21" t="str">
-        <v>Lucas Ramirez</v>
+        <v>Abigail Anderson</v>
       </c>
       <c r="D21" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E21" t="str">
-        <v>KSBC-SAV-10038792</v>
+        <v>KSBC-SAV-10052220</v>
       </c>
       <c r="F21">
-        <v>400000</v>
+        <v>4720000</v>
       </c>
       <c r="G21">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="I21" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J21" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K21">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="L21" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M21" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N21" t="str">
-        <v>Gemini Risk Score: 27/100 (LOW) for Lucas Ramirez.</v>
+        <v>Gemini Risk Score: 83/100 (HIGH) for Abigail Anderson.</v>
       </c>
       <c r="O21" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P21" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q21" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R21" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -1582,46 +1582,46 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>c0000027-1111-4111-c111-111111111111</v>
+        <v>c0000036-1111-4111-c111-111111111111</v>
       </c>
       <c r="B22" t="str">
-        <v>b0000027-1111-4111-b111-111111111111</v>
+        <v>b0000036-1111-4111-b111-111111111111</v>
       </c>
       <c r="C22" t="str">
-        <v>Charlotte Sterling</v>
+        <v>Owen Moore</v>
       </c>
       <c r="D22" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E22" t="str">
-        <v>KSBC-SAV-10040284</v>
+        <v>KSBC-SAV-10053712</v>
       </c>
       <c r="F22">
-        <v>880000</v>
+        <v>5200000</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="H22">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="I22" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J22" t="str">
-        <v>UNDERWRITING</v>
+        <v>REJECTED</v>
       </c>
       <c r="K22">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="L22" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M22" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N22" t="str">
-        <v>Gemini Risk Score: 35/100 (LOW) for Charlotte Sterling.</v>
+        <v>Gemini Risk Score: 87/100 (HIGH) for Owen Moore.</v>
       </c>
       <c r="O22" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1694,37 +1694,37 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>c0000029-1111-4111-c111-111111111111</v>
+        <v>c0000030-1111-4111-c111-111111111111</v>
       </c>
       <c r="B24" t="str">
-        <v>b0000029-1111-4111-b111-111111111111</v>
+        <v>b0000030-1111-4111-b111-111111111111</v>
       </c>
       <c r="C24" t="str">
-        <v>Amelia Sharma</v>
+        <v>Alexander Mehta</v>
       </c>
       <c r="D24" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E24" t="str">
-        <v>KSBC-SAV-10043268</v>
+        <v>KSBC-SAV-10044760</v>
       </c>
       <c r="F24">
-        <v>1840000</v>
+        <v>2320000</v>
       </c>
       <c r="G24">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="H24">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I24" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J24" t="str">
-        <v>DISBURSED</v>
+        <v>REJECTED</v>
       </c>
       <c r="K24">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L24" t="str">
         <v>MODERATE</v>
@@ -1733,16 +1733,16 @@
         <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N24" t="str">
-        <v>Gemini Risk Score: 49/100 (MODERATE) for Amelia Sharma.</v>
+        <v>Gemini Risk Score: 56/100 (MODERATE) for Alexander Mehta.</v>
       </c>
       <c r="O24" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P24" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q24" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R24" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -1750,37 +1750,37 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>c0000030-1111-4111-c111-111111111111</v>
+        <v>c0000029-1111-4111-c111-111111111111</v>
       </c>
       <c r="B25" t="str">
-        <v>b0000030-1111-4111-b111-111111111111</v>
+        <v>b0000029-1111-4111-b111-111111111111</v>
       </c>
       <c r="C25" t="str">
-        <v>Alexander Mehta</v>
+        <v>Amelia Sharma</v>
       </c>
       <c r="D25" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E25" t="str">
-        <v>KSBC-SAV-10044760</v>
+        <v>KSBC-SAV-10043268</v>
       </c>
       <c r="F25">
-        <v>2320000</v>
+        <v>1840000</v>
       </c>
       <c r="G25">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="H25">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="I25" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J25" t="str">
-        <v>REJECTED</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K25">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L25" t="str">
         <v>MODERATE</v>
@@ -1789,16 +1789,16 @@
         <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N25" t="str">
-        <v>Gemini Risk Score: 56/100 (MODERATE) for Alexander Mehta.</v>
+        <v>Gemini Risk Score: 49/100 (MODERATE) for Amelia Sharma.</v>
       </c>
       <c r="O25" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P25" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q25" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R25" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -1806,46 +1806,46 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>c0000031-1111-4111-c111-111111111111</v>
+        <v>c0000027-1111-4111-c111-111111111111</v>
       </c>
       <c r="B26" t="str">
-        <v>b0000031-1111-4111-b111-111111111111</v>
+        <v>b0000027-1111-4111-b111-111111111111</v>
       </c>
       <c r="C26" t="str">
-        <v>Harper Williams</v>
+        <v>Charlotte Sterling</v>
       </c>
       <c r="D26" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E26" t="str">
-        <v>KSBC-SAV-10046252</v>
+        <v>KSBC-SAV-10040284</v>
       </c>
       <c r="F26">
-        <v>2800000</v>
+        <v>880000</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H26">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I26" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J26" t="str">
-        <v>DRAFT</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K26">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="L26" t="str">
-        <v>MODERATE</v>
+        <v>LOW</v>
       </c>
       <c r="M26" t="str">
-        <v>CONDITIONAL_APPROVE</v>
+        <v>APPROVE</v>
       </c>
       <c r="N26" t="str">
-        <v>Gemini Risk Score: 62/100 (MODERATE) for Harper Williams.</v>
+        <v>Gemini Risk Score: 35/100 (LOW) for Charlotte Sterling.</v>
       </c>
       <c r="O26" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1862,46 +1862,46 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>c0000032-1111-4111-c111-111111111111</v>
+        <v>c0000038-1111-4111-c111-111111111111</v>
       </c>
       <c r="B27" t="str">
-        <v>b0000032-1111-4111-b111-111111111111</v>
+        <v>b0000038-1111-4111-b111-111111111111</v>
       </c>
       <c r="C27" t="str">
-        <v>Sebastian Garcia</v>
+        <v>Theodore White</v>
       </c>
       <c r="D27" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E27" t="str">
-        <v>KSBC-SAV-10047744</v>
+        <v>KSBC-SAV-10056696</v>
       </c>
       <c r="F27">
-        <v>3280000</v>
+        <v>6160000</v>
       </c>
       <c r="G27">
-        <v>9.75</v>
+        <v>8.25</v>
       </c>
       <c r="H27">
         <v>24</v>
       </c>
       <c r="I27" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J27" t="str">
         <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K27">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="L27" t="str">
-        <v>MODERATE</v>
+        <v>HIGH</v>
       </c>
       <c r="M27" t="str">
-        <v>CONDITIONAL_APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N27" t="str">
-        <v>Gemini Risk Score: 68/100 (MODERATE) for Sebastian Garcia.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Theodore White.</v>
       </c>
       <c r="O27" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1918,37 +1918,37 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>c0000033-1111-4111-c111-111111111111</v>
+        <v>c0000039-1111-4111-c111-111111111111</v>
       </c>
       <c r="B28" t="str">
-        <v>b0000033-1111-4111-b111-111111111111</v>
+        <v>b0000039-1111-4111-b111-111111111111</v>
       </c>
       <c r="C28" t="str">
-        <v>Evelyn Rodriguez</v>
+        <v>Ella Clark</v>
       </c>
       <c r="D28" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E28" t="str">
-        <v>KSBC-SAV-10049236</v>
+        <v>KSBC-SAV-10058188</v>
       </c>
       <c r="F28">
-        <v>3760000</v>
+        <v>6640000</v>
       </c>
       <c r="G28">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="H28">
         <v>36</v>
       </c>
       <c r="I28" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J28" t="str">
         <v>UNDERWRITING</v>
       </c>
       <c r="K28">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L28" t="str">
         <v>HIGH</v>
@@ -1957,7 +1957,7 @@
         <v>REJECT</v>
       </c>
       <c r="N28" t="str">
-        <v>Gemini Risk Score: 73/100 (HIGH) for Evelyn Rodriguez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Ella Clark.</v>
       </c>
       <c r="O28" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -1974,55 +1974,55 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>c0000035-1111-4111-c111-111111111111</v>
+        <v>c0000026-1111-4111-c111-111111111111</v>
       </c>
       <c r="B29" t="str">
-        <v>b0000035-1111-4111-b111-111111111111</v>
+        <v>b0000026-1111-4111-b111-111111111111</v>
       </c>
       <c r="C29" t="str">
-        <v>Abigail Anderson</v>
+        <v>Lucas Ramirez</v>
       </c>
       <c r="D29" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E29" t="str">
-        <v>KSBC-SAV-10052220</v>
+        <v>KSBC-SAV-10038792</v>
       </c>
       <c r="F29">
-        <v>4720000</v>
+        <v>400000</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="H29">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="I29" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J29" t="str">
-        <v>DISBURSED</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K29">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="L29" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M29" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N29" t="str">
-        <v>Gemini Risk Score: 83/100 (HIGH) for Abigail Anderson.</v>
+        <v>Gemini Risk Score: 27/100 (LOW) for Lucas Ramirez.</v>
       </c>
       <c r="O29" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P29" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q29" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R29" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -2030,37 +2030,37 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>c0000036-1111-4111-c111-111111111111</v>
+        <v>c0000034-1111-4111-c111-111111111111</v>
       </c>
       <c r="B30" t="str">
-        <v>b0000036-1111-4111-b111-111111111111</v>
+        <v>b0000034-1111-4111-b111-111111111111</v>
       </c>
       <c r="C30" t="str">
-        <v>Owen Moore</v>
+        <v>Jack Lopez</v>
       </c>
       <c r="D30" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E30" t="str">
-        <v>KSBC-SAV-10053712</v>
+        <v>KSBC-SAV-10050728</v>
       </c>
       <c r="F30">
-        <v>5200000</v>
+        <v>4240000</v>
       </c>
       <c r="G30">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
       <c r="H30">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="I30" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J30" t="str">
-        <v>REJECTED</v>
+        <v>APPROVED</v>
       </c>
       <c r="K30">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="L30" t="str">
         <v>HIGH</v>
@@ -2069,13 +2069,13 @@
         <v>REJECT</v>
       </c>
       <c r="N30" t="str">
-        <v>Gemini Risk Score: 87/100 (HIGH) for Owen Moore.</v>
+        <v>Gemini Risk Score: 78/100 (HIGH) for Jack Lopez.</v>
       </c>
       <c r="O30" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P30" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q30" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -2086,37 +2086,37 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>c0000037-1111-4111-c111-111111111111</v>
+        <v>c0000025-1111-4111-c111-111111111111</v>
       </c>
       <c r="B31" t="str">
-        <v>b0000037-1111-4111-b111-111111111111</v>
+        <v>b0000025-1111-4111-b111-111111111111</v>
       </c>
       <c r="C31" t="str">
-        <v>Emily Lee</v>
+        <v>Mia Harris</v>
       </c>
       <c r="D31" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E31" t="str">
-        <v>KSBC-SAV-10055204</v>
+        <v>KSBC-SAV-10037300</v>
       </c>
       <c r="F31">
-        <v>5680000</v>
+        <v>11920000</v>
       </c>
       <c r="G31">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H31">
         <v>12</v>
       </c>
       <c r="I31" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J31" t="str">
         <v>DRAFT</v>
       </c>
       <c r="K31">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L31" t="str">
         <v>HIGH</v>
@@ -2125,7 +2125,7 @@
         <v>REJECT</v>
       </c>
       <c r="N31" t="str">
-        <v>Gemini Risk Score: 92/100 (HIGH) for Emily Lee.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Mia Harris.</v>
       </c>
       <c r="O31" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2142,34 +2142,34 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>c0000038-1111-4111-c111-111111111111</v>
+        <v>c0000022-1111-4111-c111-111111111111</v>
       </c>
       <c r="B32" t="str">
-        <v>b0000038-1111-4111-b111-111111111111</v>
+        <v>b0000022-1111-4111-b111-111111111111</v>
       </c>
       <c r="C32" t="str">
-        <v>Theodore White</v>
+        <v>William Thomas</v>
       </c>
       <c r="D32" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E32" t="str">
-        <v>KSBC-SAV-10056696</v>
+        <v>KSBC-SAV-10032824</v>
       </c>
       <c r="F32">
-        <v>6160000</v>
+        <v>10480000</v>
       </c>
       <c r="G32">
         <v>8.25</v>
       </c>
       <c r="H32">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="I32" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J32" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K32">
         <v>94</v>
@@ -2181,16 +2181,16 @@
         <v>REJECT</v>
       </c>
       <c r="N32" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Theodore White.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for William Thomas.</v>
       </c>
       <c r="O32" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P32" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q32" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a7777777-7777-4777-a777-777777777777</v>
       </c>
       <c r="R32" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -2198,34 +2198,34 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>c0000039-1111-4111-c111-111111111111</v>
+        <v>c0000023-1111-4111-c111-111111111111</v>
       </c>
       <c r="B33" t="str">
-        <v>b0000039-1111-4111-b111-111111111111</v>
+        <v>b0000023-1111-4111-b111-111111111111</v>
       </c>
       <c r="C33" t="str">
-        <v>Ella Clark</v>
+        <v>Ava Jackson</v>
       </c>
       <c r="D33" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E33" t="str">
-        <v>KSBC-SAV-10058188</v>
+        <v>KSBC-SAV-10034316</v>
       </c>
       <c r="F33">
-        <v>6640000</v>
+        <v>10960000</v>
       </c>
       <c r="G33">
         <v>9</v>
       </c>
       <c r="H33">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="I33" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J33" t="str">
-        <v>UNDERWRITING</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K33">
         <v>94</v>
@@ -2237,16 +2237,16 @@
         <v>REJECT</v>
       </c>
       <c r="N33" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ella Clark.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Ava Jackson.</v>
       </c>
       <c r="O33" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P33" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q33" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R33" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -2254,37 +2254,37 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>c0000022-1111-4111-c111-111111111111</v>
+        <v>c0000037-1111-4111-c111-111111111111</v>
       </c>
       <c r="B34" t="str">
-        <v>b0000022-1111-4111-b111-111111111111</v>
+        <v>b0000037-1111-4111-b111-111111111111</v>
       </c>
       <c r="C34" t="str">
-        <v>William Thomas</v>
+        <v>Emily Lee</v>
       </c>
       <c r="D34" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E34" t="str">
-        <v>KSBC-SAV-10032824</v>
+        <v>KSBC-SAV-10055204</v>
       </c>
       <c r="F34">
-        <v>10480000</v>
+        <v>5680000</v>
       </c>
       <c r="G34">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="H34">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I34" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J34" t="str">
-        <v>DISBURSED</v>
+        <v>DRAFT</v>
       </c>
       <c r="K34">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L34" t="str">
         <v>HIGH</v>
@@ -2293,16 +2293,16 @@
         <v>REJECT</v>
       </c>
       <c r="N34" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for William Thomas.</v>
+        <v>Gemini Risk Score: 92/100 (HIGH) for Emily Lee.</v>
       </c>
       <c r="O34" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P34" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q34" t="str">
-        <v>a7777777-7777-4777-a777-777777777777</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R34" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -2310,34 +2310,34 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>c0000006-1111-4111-c111-111111111111</v>
+        <v>c0000016-1111-4111-c111-111111111111</v>
       </c>
       <c r="B35" t="str">
-        <v>b0000006-1111-4111-b111-111111111111</v>
+        <v>b0000016-1111-4111-b111-111111111111</v>
       </c>
       <c r="C35" t="str">
-        <v>Rachel Davis</v>
+        <v>Daniel Patel</v>
       </c>
       <c r="D35" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E35" t="str">
-        <v>KSBC-SAV-10008952</v>
+        <v>KSBC-SAV-10023872</v>
       </c>
       <c r="F35">
-        <v>2800000</v>
+        <v>7600000</v>
       </c>
       <c r="G35">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="H35">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="I35" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J35" t="str">
-        <v>REJECTED</v>
+        <v>APPROVED</v>
       </c>
       <c r="K35">
         <v>94</v>
@@ -2349,13 +2349,13 @@
         <v>REJECT</v>
       </c>
       <c r="N35" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Daniel Patel.</v>
       </c>
       <c r="O35" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P35" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q35" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -2366,34 +2366,34 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>c0000005-1111-4111-c111-111111111111</v>
+        <v>c0000001-1111-4111-c111-111111111111</v>
       </c>
       <c r="B36" t="str">
-        <v>b0000005-1111-4111-b111-111111111111</v>
+        <v>b0000001-1111-4111-b111-111111111111</v>
       </c>
       <c r="C36" t="str">
-        <v>Marcus Jones</v>
+        <v>Alexander Chen</v>
       </c>
       <c r="D36" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E36" t="str">
-        <v>KSBC-SAV-10007460</v>
+        <v>KSBC-SAV-10001492</v>
       </c>
       <c r="F36">
-        <v>2320000</v>
+        <v>400000</v>
       </c>
       <c r="G36">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H36">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I36" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J36" t="str">
-        <v>DISBURSED</v>
+        <v>DRAFT</v>
       </c>
       <c r="K36">
         <v>94</v>
@@ -2405,16 +2405,16 @@
         <v>REJECT</v>
       </c>
       <c r="N36" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
       </c>
       <c r="O36" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P36" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q36" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R36" t="str">
         <v>2026-07-29T15:27:02.612077+00:00</v>
@@ -2422,34 +2422,34 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>c0000004-1111-4111-c111-111111111111</v>
+        <v>c0000002-1111-4111-c111-111111111111</v>
       </c>
       <c r="B37" t="str">
-        <v>b0000004-1111-4111-b111-111111111111</v>
+        <v>b0000002-1111-4111-b111-111111111111</v>
       </c>
       <c r="C37" t="str">
-        <v>Elena Smith</v>
+        <v>Sarah Green</v>
       </c>
       <c r="D37" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E37" t="str">
-        <v>KSBC-SAV-10005968</v>
+        <v>KSBC-SAV-10002984</v>
       </c>
       <c r="F37">
-        <v>1840000</v>
+        <v>880000</v>
       </c>
       <c r="G37">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
       <c r="H37">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="I37" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J37" t="str">
-        <v>APPROVED</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K37">
         <v>94</v>
@@ -2461,13 +2461,13 @@
         <v>REJECT</v>
       </c>
       <c r="N37" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
       </c>
       <c r="O37" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P37" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q37" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -2478,34 +2478,34 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>c0000015-1111-4111-c111-111111111111</v>
+        <v>c0000018-1111-4111-c111-111111111111</v>
       </c>
       <c r="B38" t="str">
-        <v>b0000015-1111-4111-b111-111111111111</v>
+        <v>b0000018-1111-4111-b111-111111111111</v>
       </c>
       <c r="C38" t="str">
-        <v>Amanda Vance</v>
+        <v>James Brown</v>
       </c>
       <c r="D38" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E38" t="str">
-        <v>KSBC-SAV-10022380</v>
+        <v>KSBC-SAV-10026856</v>
       </c>
       <c r="F38">
-        <v>7120000</v>
+        <v>8560000</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="H38">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="I38" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J38" t="str">
-        <v>UNDERWRITING</v>
+        <v>REJECTED</v>
       </c>
       <c r="K38">
         <v>94</v>
@@ -2517,7 +2517,7 @@
         <v>REJECT</v>
       </c>
       <c r="N38" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Amanda Vance.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for James Brown.</v>
       </c>
       <c r="O38" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2534,34 +2534,34 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>c0000016-1111-4111-c111-111111111111</v>
+        <v>c0000017-1111-4111-c111-111111111111</v>
       </c>
       <c r="B39" t="str">
-        <v>b0000016-1111-4111-b111-111111111111</v>
+        <v>b0000017-1111-4111-b111-111111111111</v>
       </c>
       <c r="C39" t="str">
-        <v>Daniel Patel</v>
+        <v>Sophia Johnson</v>
       </c>
       <c r="D39" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E39" t="str">
-        <v>KSBC-SAV-10023872</v>
+        <v>KSBC-SAV-10025364</v>
       </c>
       <c r="F39">
-        <v>7600000</v>
+        <v>8080000</v>
       </c>
       <c r="G39">
-        <v>9.75</v>
+        <v>4.5</v>
       </c>
       <c r="H39">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I39" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J39" t="str">
-        <v>APPROVED</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K39">
         <v>94</v>
@@ -2573,7 +2573,7 @@
         <v>REJECT</v>
       </c>
       <c r="N39" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Daniel Patel.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Sophia Johnson.</v>
       </c>
       <c r="O39" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2582,7 +2582,7 @@
         <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q39" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R39" t="str">
         <v>2026-07-29T15:27:02.612077+00:00</v>
@@ -2590,34 +2590,34 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>c0000017-1111-4111-c111-111111111111</v>
+        <v>c0000019-1111-4111-c111-111111111111</v>
       </c>
       <c r="B40" t="str">
-        <v>b0000017-1111-4111-b111-111111111111</v>
+        <v>b0000019-1111-4111-b111-111111111111</v>
       </c>
       <c r="C40" t="str">
-        <v>Sophia Johnson</v>
+        <v>Olivia Miller</v>
       </c>
       <c r="D40" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E40" t="str">
-        <v>KSBC-SAV-10025364</v>
+        <v>KSBC-SAV-10028348</v>
       </c>
       <c r="F40">
-        <v>8080000</v>
+        <v>9040000</v>
       </c>
       <c r="G40">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H40">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I40" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J40" t="str">
-        <v>DISBURSED</v>
+        <v>DRAFT</v>
       </c>
       <c r="K40">
         <v>94</v>
@@ -2629,16 +2629,16 @@
         <v>REJECT</v>
       </c>
       <c r="N40" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Sophia Johnson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Olivia Miller.</v>
       </c>
       <c r="O40" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P40" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q40" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R40" t="str">
         <v>2026-07-29T15:27:02.612077+00:00</v>
@@ -2646,46 +2646,46 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>c0000018-1111-4111-c111-111111111111</v>
+        <v>c0000014-1111-4111-c111-111111111111</v>
       </c>
       <c r="B41" t="str">
-        <v>b0000018-1111-4111-b111-111111111111</v>
+        <v>b0000014-1111-4111-b111-111111111111</v>
       </c>
       <c r="C41" t="str">
-        <v>James Brown</v>
+        <v>Christopher Jenkins</v>
       </c>
       <c r="D41" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E41" t="str">
-        <v>KSBC-SAV-10026856</v>
+        <v>KSBC-SAV-10020888</v>
       </c>
       <c r="F41">
-        <v>8560000</v>
+        <v>6640000</v>
       </c>
       <c r="G41">
-        <v>5.25</v>
+        <v>8.25</v>
       </c>
       <c r="H41">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="I41" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J41" t="str">
-        <v>REJECTED</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K41">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L41" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M41" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N41" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for James Brown.</v>
+        <v>Applicant David Reddy (Account: KSBC-SAV-10049281) evaluated under baseline AI underwriting parameters.</v>
       </c>
       <c r="O41" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2702,34 +2702,34 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>c0000019-1111-4111-c111-111111111111</v>
+        <v>c0000004-1111-4111-c111-111111111111</v>
       </c>
       <c r="B42" t="str">
-        <v>b0000019-1111-4111-b111-111111111111</v>
+        <v>b0000004-1111-4111-b111-111111111111</v>
       </c>
       <c r="C42" t="str">
-        <v>Olivia Miller</v>
+        <v>Elena Smith</v>
       </c>
       <c r="D42" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E42" t="str">
-        <v>KSBC-SAV-10028348</v>
+        <v>KSBC-SAV-10005968</v>
       </c>
       <c r="F42">
-        <v>9040000</v>
+        <v>1840000</v>
       </c>
       <c r="G42">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="H42">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="I42" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J42" t="str">
-        <v>DRAFT</v>
+        <v>APPROVED</v>
       </c>
       <c r="K42">
         <v>94</v>
@@ -2741,13 +2741,13 @@
         <v>REJECT</v>
       </c>
       <c r="N42" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Olivia Miller.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
       </c>
       <c r="O42" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P42" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q42" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -2758,34 +2758,34 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>c0000020-1111-4111-c111-111111111111</v>
+        <v>c0000003-1111-4111-c111-111111111111</v>
       </c>
       <c r="B43" t="str">
-        <v>b0000020-1111-4111-b111-111111111111</v>
+        <v>b0000003-1111-4111-b111-111111111111</v>
       </c>
       <c r="C43" t="str">
-        <v>Ethan Martinez</v>
+        <v>David Reddy</v>
       </c>
       <c r="D43" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E43" t="str">
-        <v>KSBC-SAV-10029840</v>
+        <v>KSBC-SAV-10004476</v>
       </c>
       <c r="F43">
-        <v>9520000</v>
+        <v>1360000</v>
       </c>
       <c r="G43">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="H43">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I43" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J43" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K43">
         <v>94</v>
@@ -2797,7 +2797,7 @@
         <v>REJECT</v>
       </c>
       <c r="N43" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ethan Martinez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for David Reddy.</v>
       </c>
       <c r="O43" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2814,34 +2814,34 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>c0000003-1111-4111-c111-111111111111</v>
+        <v>c0000005-1111-4111-c111-111111111111</v>
       </c>
       <c r="B44" t="str">
-        <v>b0000003-1111-4111-b111-111111111111</v>
+        <v>b0000005-1111-4111-b111-111111111111</v>
       </c>
       <c r="C44" t="str">
-        <v>David Reddy</v>
+        <v>Marcus Jones</v>
       </c>
       <c r="D44" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E44" t="str">
-        <v>KSBC-SAV-10004476</v>
+        <v>KSBC-SAV-10007460</v>
       </c>
       <c r="F44">
-        <v>1360000</v>
+        <v>2320000</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H44">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="I44" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J44" t="str">
-        <v>UNDERWRITING</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K44">
         <v>94</v>
@@ -2853,16 +2853,16 @@
         <v>REJECT</v>
       </c>
       <c r="N44" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for David Reddy.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
       </c>
       <c r="O44" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P44" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q44" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R44" t="str">
         <v>2026-07-29T15:27:02.612077+00:00</v>
@@ -2870,34 +2870,34 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>c0000002-1111-4111-c111-111111111111</v>
+        <v>c0000015-1111-4111-c111-111111111111</v>
       </c>
       <c r="B45" t="str">
-        <v>b0000002-1111-4111-b111-111111111111</v>
+        <v>b0000015-1111-4111-b111-111111111111</v>
       </c>
       <c r="C45" t="str">
-        <v>Sarah Green</v>
+        <v>Amanda Vance</v>
       </c>
       <c r="D45" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E45" t="str">
-        <v>KSBC-SAV-10002984</v>
+        <v>KSBC-SAV-10022380</v>
       </c>
       <c r="F45">
-        <v>880000</v>
+        <v>7120000</v>
       </c>
       <c r="G45">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="H45">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I45" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J45" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K45">
         <v>94</v>
@@ -2909,7 +2909,7 @@
         <v>REJECT</v>
       </c>
       <c r="N45" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Amanda Vance.</v>
       </c>
       <c r="O45" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2926,34 +2926,34 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>c0000001-1111-4111-c111-111111111111</v>
+        <v>c0000012-1111-4111-c111-111111111111</v>
       </c>
       <c r="B46" t="str">
-        <v>b0000001-1111-4111-b111-111111111111</v>
+        <v>b0000012-1111-4111-b111-111111111111</v>
       </c>
       <c r="C46" t="str">
-        <v>Alexander Chen</v>
+        <v>Jessica Sanchez</v>
       </c>
       <c r="D46" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E46" t="str">
-        <v>KSBC-SAV-10001492</v>
+        <v>KSBC-SAV-10017904</v>
       </c>
       <c r="F46">
-        <v>400000</v>
+        <v>5680000</v>
       </c>
       <c r="G46">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="H46">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="I46" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J46" t="str">
-        <v>DRAFT</v>
+        <v>REJECTED</v>
       </c>
       <c r="K46">
         <v>94</v>
@@ -2965,7 +2965,7 @@
         <v>REJECT</v>
       </c>
       <c r="N46" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Jessica Sanchez.</v>
       </c>
       <c r="O46" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -2982,34 +2982,34 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>c0000014-1111-4111-c111-111111111111</v>
+        <v>c0000011-1111-4111-c111-111111111111</v>
       </c>
       <c r="B47" t="str">
-        <v>b0000014-1111-4111-b111-111111111111</v>
+        <v>b0000011-1111-4111-b111-111111111111</v>
       </c>
       <c r="C47" t="str">
-        <v>Christopher Jenkins</v>
+        <v>Michael Thompson</v>
       </c>
       <c r="D47" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E47" t="str">
-        <v>KSBC-SAV-10020888</v>
+        <v>KSBC-SAV-10016412</v>
       </c>
       <c r="F47">
-        <v>6640000</v>
+        <v>5200000</v>
       </c>
       <c r="G47">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="H47">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="I47" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J47" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>DISBURSED</v>
       </c>
       <c r="K47">
         <v>94</v>
@@ -3021,16 +3021,16 @@
         <v>REJECT</v>
       </c>
       <c r="N47" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Christopher Jenkins.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Michael Thompson.</v>
       </c>
       <c r="O47" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P47" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q47" t="str">
-        <v>Pending Treasury Disbursement</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R47" t="str">
         <v>2026-07-29T15:27:02.612077+00:00</v>
@@ -3038,34 +3038,34 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>c0000013-1111-4111-c111-111111111111</v>
+        <v>c0000010-1111-4111-c111-111111111111</v>
       </c>
       <c r="B48" t="str">
-        <v>b0000013-1111-4111-b111-111111111111</v>
+        <v>b0000010-1111-4111-b111-111111111111</v>
       </c>
       <c r="C48" t="str">
-        <v>Emily Lewis</v>
+        <v>Rohan Martin</v>
       </c>
       <c r="D48" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E48" t="str">
-        <v>KSBC-SAV-10019396</v>
+        <v>KSBC-SAV-10014920</v>
       </c>
       <c r="F48">
-        <v>6160000</v>
+        <v>4720000</v>
       </c>
       <c r="G48">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="H48">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="I48" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J48" t="str">
-        <v>DRAFT</v>
+        <v>APPROVED</v>
       </c>
       <c r="K48">
         <v>94</v>
@@ -3077,13 +3077,13 @@
         <v>REJECT</v>
       </c>
       <c r="N48" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Emily Lewis.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rohan Martin.</v>
       </c>
       <c r="O48" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P48" t="str">
-        <v>Pending Executive Review</v>
+        <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q48" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -3094,31 +3094,31 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>c0000012-1111-4111-c111-111111111111</v>
+        <v>c0000006-1111-4111-c111-111111111111</v>
       </c>
       <c r="B49" t="str">
-        <v>b0000012-1111-4111-b111-111111111111</v>
+        <v>b0000006-1111-4111-b111-111111111111</v>
       </c>
       <c r="C49" t="str">
-        <v>Jessica Sanchez</v>
+        <v>Rachel Davis</v>
       </c>
       <c r="D49" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E49" t="str">
-        <v>KSBC-SAV-10017904</v>
+        <v>KSBC-SAV-10008952</v>
       </c>
       <c r="F49">
-        <v>5680000</v>
+        <v>2800000</v>
       </c>
       <c r="G49">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="H49">
         <v>240</v>
       </c>
       <c r="I49" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J49" t="str">
         <v>REJECTED</v>
@@ -3133,7 +3133,7 @@
         <v>REJECT</v>
       </c>
       <c r="N49" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Jessica Sanchez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
       </c>
       <c r="O49" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3150,34 +3150,34 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>c0000011-1111-4111-c111-111111111111</v>
+        <v>c0000008-1111-4111-c111-111111111111</v>
       </c>
       <c r="B50" t="str">
-        <v>b0000011-1111-4111-b111-111111111111</v>
+        <v>b0000008-1111-4111-b111-111111111111</v>
       </c>
       <c r="C50" t="str">
-        <v>Michael Thompson</v>
+        <v>Priya Wilson</v>
       </c>
       <c r="D50" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E50" t="str">
-        <v>KSBC-SAV-10016412</v>
+        <v>KSBC-SAV-10011936</v>
       </c>
       <c r="F50">
-        <v>5200000</v>
+        <v>3760000</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>9.75</v>
       </c>
       <c r="H50">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="I50" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J50" t="str">
-        <v>DISBURSED</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K50">
         <v>94</v>
@@ -3189,16 +3189,16 @@
         <v>REJECT</v>
       </c>
       <c r="N50" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Michael Thompson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
       </c>
       <c r="O50" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P50" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q50" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>Pending Treasury Disbursement</v>
       </c>
       <c r="R50" t="str">
         <v>2026-07-29T15:27:02.612077+00:00</v>
@@ -3206,34 +3206,34 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>c0000010-1111-4111-c111-111111111111</v>
+        <v>c0000007-1111-4111-c111-111111111111</v>
       </c>
       <c r="B51" t="str">
-        <v>b0000010-1111-4111-b111-111111111111</v>
+        <v>b0000007-1111-4111-b111-111111111111</v>
       </c>
       <c r="C51" t="str">
-        <v>Rohan Martin</v>
+        <v>Vikram Hernandez</v>
       </c>
       <c r="D51" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E51" t="str">
-        <v>KSBC-SAV-10014920</v>
+        <v>KSBC-SAV-10010444</v>
       </c>
       <c r="F51">
-        <v>4720000</v>
+        <v>3280000</v>
       </c>
       <c r="G51">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="H51">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I51" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J51" t="str">
-        <v>APPROVED</v>
+        <v>DRAFT</v>
       </c>
       <c r="K51">
         <v>94</v>
@@ -3245,13 +3245,13 @@
         <v>REJECT</v>
       </c>
       <c r="N51" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rohan Martin.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Vikram Hernandez.</v>
       </c>
       <c r="O51" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
       </c>
       <c r="P51" t="str">
-        <v>a4444444-4444-4444-a444-444444444444</v>
+        <v>Pending Executive Review</v>
       </c>
       <c r="Q51" t="str">
         <v>Pending Treasury Disbursement</v>
@@ -3262,46 +3262,46 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>c0000009-1111-4111-c111-111111111111</v>
+        <v>c0000020-1111-4111-c111-111111111111</v>
       </c>
       <c r="B52" t="str">
-        <v>b0000009-1111-4111-b111-111111111111</v>
+        <v>b0000020-1111-4111-b111-111111111111</v>
       </c>
       <c r="C52" t="str">
-        <v>Ananya Taylor</v>
+        <v>Ethan Martinez</v>
       </c>
       <c r="D52" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E52" t="str">
-        <v>KSBC-SAV-10013428</v>
+        <v>KSBC-SAV-10029840</v>
       </c>
       <c r="F52">
-        <v>4240000</v>
+        <v>9520000</v>
       </c>
       <c r="G52">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="H52">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I52" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J52" t="str">
         <v>UNDERWRITING</v>
       </c>
       <c r="K52">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L52" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M52" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N52" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ananya Taylor.</v>
+        <v>Applicant David Reddy (Account: KSBC-SAV-10049281) evaluated under baseline AI underwriting parameters.</v>
       </c>
       <c r="O52" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3318,34 +3318,34 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>c0000008-1111-4111-c111-111111111111</v>
+        <v>c0000009-1111-4111-c111-111111111111</v>
       </c>
       <c r="B53" t="str">
-        <v>b0000008-1111-4111-b111-111111111111</v>
+        <v>b0000009-1111-4111-b111-111111111111</v>
       </c>
       <c r="C53" t="str">
-        <v>Priya Wilson</v>
+        <v>Ananya Taylor</v>
       </c>
       <c r="D53" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E53" t="str">
-        <v>KSBC-SAV-10011936</v>
+        <v>KSBC-SAV-10013428</v>
       </c>
       <c r="F53">
-        <v>3760000</v>
+        <v>4240000</v>
       </c>
       <c r="G53">
-        <v>9.75</v>
+        <v>4.5</v>
       </c>
       <c r="H53">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I53" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J53" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K53">
         <v>94</v>
@@ -3357,7 +3357,7 @@
         <v>REJECT</v>
       </c>
       <c r="N53" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Ananya Taylor.</v>
       </c>
       <c r="O53" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3374,31 +3374,31 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>c0000007-1111-4111-c111-111111111111</v>
+        <v>c0000013-1111-4111-c111-111111111111</v>
       </c>
       <c r="B54" t="str">
-        <v>b0000007-1111-4111-b111-111111111111</v>
+        <v>b0000013-1111-4111-b111-111111111111</v>
       </c>
       <c r="C54" t="str">
-        <v>Vikram Hernandez</v>
+        <v>Emily Lewis</v>
       </c>
       <c r="D54" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E54" t="str">
-        <v>KSBC-SAV-10010444</v>
+        <v>KSBC-SAV-10019396</v>
       </c>
       <c r="F54">
-        <v>3280000</v>
+        <v>6160000</v>
       </c>
       <c r="G54">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H54">
         <v>12</v>
       </c>
       <c r="I54" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J54" t="str">
         <v>DRAFT</v>
@@ -3413,7 +3413,7 @@
         <v>REJECT</v>
       </c>
       <c r="N54" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Vikram Hernandez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Emily Lewis.</v>
       </c>
       <c r="O54" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3553,46 +3553,46 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c0000041-1111-4111-c111-111111111111</v>
+        <v>c0000053-1111-4111-c111-111111111111</v>
       </c>
       <c r="B2" t="str">
-        <v>b0000041-1111-4111-b111-111111111111</v>
+        <v>b0000053-1111-4111-b111-111111111111</v>
       </c>
       <c r="C2" t="str">
-        <v>Alexander Chen</v>
+        <v>Emily Lewis</v>
       </c>
       <c r="D2" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E2" t="str">
-        <v>KSBC-SAV-10061172</v>
+        <v>KSBC-SAV-10079076</v>
       </c>
       <c r="F2">
-        <v>7600000</v>
+        <v>1360000</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H2">
         <v>120</v>
       </c>
       <c r="I2" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J2" t="str">
         <v>DISBURSED</v>
       </c>
       <c r="K2">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="L2" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M2" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N2" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
+        <v>Gemini Risk Score: 32/100 (LOW) for Emily Lewis.</v>
       </c>
       <c r="O2" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3609,46 +3609,46 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c0000053-1111-4111-c111-111111111111</v>
+        <v>c0000041-1111-4111-c111-111111111111</v>
       </c>
       <c r="B3" t="str">
-        <v>b0000053-1111-4111-b111-111111111111</v>
+        <v>b0000041-1111-4111-b111-111111111111</v>
       </c>
       <c r="C3" t="str">
-        <v>Emily Lewis</v>
+        <v>Alexander Chen</v>
       </c>
       <c r="D3" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E3" t="str">
-        <v>KSBC-SAV-10079076</v>
+        <v>KSBC-SAV-10061172</v>
       </c>
       <c r="F3">
-        <v>1360000</v>
+        <v>7600000</v>
       </c>
       <c r="G3">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
         <v>120</v>
       </c>
       <c r="I3" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J3" t="str">
         <v>DISBURSED</v>
       </c>
       <c r="K3">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="L3" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M3" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N3" t="str">
-        <v>Gemini Risk Score: 32/100 (LOW) for Emily Lewis.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
       </c>
       <c r="O3" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3721,37 +3721,37 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>c0000023-1111-4111-c111-111111111111</v>
+        <v>c0000035-1111-4111-c111-111111111111</v>
       </c>
       <c r="B5" t="str">
-        <v>b0000023-1111-4111-b111-111111111111</v>
+        <v>b0000035-1111-4111-b111-111111111111</v>
       </c>
       <c r="C5" t="str">
-        <v>Ava Jackson</v>
+        <v>Abigail Anderson</v>
       </c>
       <c r="D5" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E5" t="str">
-        <v>KSBC-SAV-10034316</v>
+        <v>KSBC-SAV-10052220</v>
       </c>
       <c r="F5">
-        <v>10960000</v>
+        <v>4720000</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>120</v>
       </c>
       <c r="I5" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J5" t="str">
         <v>DISBURSED</v>
       </c>
       <c r="K5">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="L5" t="str">
         <v>HIGH</v>
@@ -3760,7 +3760,7 @@
         <v>REJECT</v>
       </c>
       <c r="N5" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ava Jackson.</v>
+        <v>Gemini Risk Score: 83/100 (HIGH) for Abigail Anderson.</v>
       </c>
       <c r="O5" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3833,37 +3833,37 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c0000035-1111-4111-c111-111111111111</v>
+        <v>c0000022-1111-4111-c111-111111111111</v>
       </c>
       <c r="B7" t="str">
-        <v>b0000035-1111-4111-b111-111111111111</v>
+        <v>b0000022-1111-4111-b111-111111111111</v>
       </c>
       <c r="C7" t="str">
-        <v>Abigail Anderson</v>
+        <v>William Thomas</v>
       </c>
       <c r="D7" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E7" t="str">
-        <v>KSBC-SAV-10052220</v>
+        <v>KSBC-SAV-10032824</v>
       </c>
       <c r="F7">
-        <v>4720000</v>
+        <v>10480000</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>8.25</v>
       </c>
       <c r="H7">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I7" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J7" t="str">
         <v>DISBURSED</v>
       </c>
       <c r="K7">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="L7" t="str">
         <v>HIGH</v>
@@ -3872,7 +3872,7 @@
         <v>REJECT</v>
       </c>
       <c r="N7" t="str">
-        <v>Gemini Risk Score: 83/100 (HIGH) for Abigail Anderson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for William Thomas.</v>
       </c>
       <c r="O7" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3881,7 +3881,7 @@
         <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q7" t="str">
-        <v>a5555555-5555-4555-a555-555555555555</v>
+        <v>a7777777-7777-4777-a777-777777777777</v>
       </c>
       <c r="R7" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -3889,31 +3889,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>c0000022-1111-4111-c111-111111111111</v>
+        <v>c0000023-1111-4111-c111-111111111111</v>
       </c>
       <c r="B8" t="str">
-        <v>b0000022-1111-4111-b111-111111111111</v>
+        <v>b0000023-1111-4111-b111-111111111111</v>
       </c>
       <c r="C8" t="str">
-        <v>William Thomas</v>
+        <v>Ava Jackson</v>
       </c>
       <c r="D8" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E8" t="str">
-        <v>KSBC-SAV-10032824</v>
+        <v>KSBC-SAV-10034316</v>
       </c>
       <c r="F8">
-        <v>10480000</v>
+        <v>10960000</v>
       </c>
       <c r="G8">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I8" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J8" t="str">
         <v>DISBURSED</v>
@@ -3928,7 +3928,7 @@
         <v>REJECT</v>
       </c>
       <c r="N8" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for William Thomas.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Ava Jackson.</v>
       </c>
       <c r="O8" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -3937,7 +3937,7 @@
         <v>a4444444-4444-4444-a444-444444444444</v>
       </c>
       <c r="Q8" t="str">
-        <v>a7777777-7777-4777-a777-777777777777</v>
+        <v>a5555555-5555-4555-a555-555555555555</v>
       </c>
       <c r="R8" t="str">
         <v>2026-07-29T15:27:02.735094+00:00</v>
@@ -3945,31 +3945,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>c0000005-1111-4111-c111-111111111111</v>
+        <v>c0000017-1111-4111-c111-111111111111</v>
       </c>
       <c r="B9" t="str">
-        <v>b0000005-1111-4111-b111-111111111111</v>
+        <v>b0000017-1111-4111-b111-111111111111</v>
       </c>
       <c r="C9" t="str">
-        <v>Marcus Jones</v>
+        <v>Sophia Johnson</v>
       </c>
       <c r="D9" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E9" t="str">
-        <v>KSBC-SAV-10007460</v>
+        <v>KSBC-SAV-10025364</v>
       </c>
       <c r="F9">
-        <v>2320000</v>
+        <v>8080000</v>
       </c>
       <c r="G9">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="H9">
         <v>120</v>
       </c>
       <c r="I9" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J9" t="str">
         <v>DISBURSED</v>
@@ -3984,7 +3984,7 @@
         <v>REJECT</v>
       </c>
       <c r="N9" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Sophia Johnson.</v>
       </c>
       <c r="O9" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4001,31 +4001,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>c0000017-1111-4111-c111-111111111111</v>
+        <v>c0000005-1111-4111-c111-111111111111</v>
       </c>
       <c r="B10" t="str">
-        <v>b0000017-1111-4111-b111-111111111111</v>
+        <v>b0000005-1111-4111-b111-111111111111</v>
       </c>
       <c r="C10" t="str">
-        <v>Sophia Johnson</v>
+        <v>Marcus Jones</v>
       </c>
       <c r="D10" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E10" t="str">
-        <v>KSBC-SAV-10025364</v>
+        <v>KSBC-SAV-10007460</v>
       </c>
       <c r="F10">
-        <v>8080000</v>
+        <v>2320000</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H10">
         <v>120</v>
       </c>
       <c r="I10" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J10" t="str">
         <v>DISBURSED</v>
@@ -4040,7 +4040,7 @@
         <v>REJECT</v>
       </c>
       <c r="N10" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Sophia Johnson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
       </c>
       <c r="O10" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4236,46 +4236,46 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c0000052-1111-4111-c111-111111111111</v>
+        <v>c0000046-1111-4111-c111-111111111111</v>
       </c>
       <c r="B2" t="str">
-        <v>b0000052-1111-4111-b111-111111111111</v>
+        <v>b0000046-1111-4111-b111-111111111111</v>
       </c>
       <c r="C2" t="str">
-        <v>Jessica Sanchez</v>
+        <v>Rachel Davis</v>
       </c>
       <c r="D2" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E2" t="str">
-        <v>KSBC-SAV-10077584</v>
+        <v>KSBC-SAV-10068632</v>
       </c>
       <c r="F2">
-        <v>880000</v>
+        <v>10000000</v>
       </c>
       <c r="G2">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="H2">
         <v>60</v>
       </c>
       <c r="I2" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J2" t="str">
         <v>APPROVED</v>
       </c>
       <c r="K2">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="L2" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M2" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N2" t="str">
-        <v>Gemini Risk Score: 28/100 (LOW) for Jessica Sanchez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
       </c>
       <c r="O2" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4292,46 +4292,46 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c0000046-1111-4111-c111-111111111111</v>
+        <v>c0000052-1111-4111-c111-111111111111</v>
       </c>
       <c r="B3" t="str">
-        <v>b0000046-1111-4111-b111-111111111111</v>
+        <v>b0000052-1111-4111-b111-111111111111</v>
       </c>
       <c r="C3" t="str">
-        <v>Rachel Davis</v>
+        <v>Jessica Sanchez</v>
       </c>
       <c r="D3" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E3" t="str">
-        <v>KSBC-SAV-10068632</v>
+        <v>KSBC-SAV-10077584</v>
       </c>
       <c r="F3">
-        <v>10000000</v>
+        <v>880000</v>
       </c>
       <c r="G3">
-        <v>8.25</v>
+        <v>6.75</v>
       </c>
       <c r="H3">
         <v>60</v>
       </c>
       <c r="I3" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J3" t="str">
         <v>APPROVED</v>
       </c>
       <c r="K3">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="L3" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M3" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N3" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
+        <v>Gemini Risk Score: 28/100 (LOW) for Jessica Sanchez.</v>
       </c>
       <c r="O3" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4348,46 +4348,46 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>c0000034-1111-4111-c111-111111111111</v>
+        <v>c0000028-1111-4111-c111-111111111111</v>
       </c>
       <c r="B4" t="str">
-        <v>b0000034-1111-4111-b111-111111111111</v>
+        <v>b0000028-1111-4111-b111-111111111111</v>
       </c>
       <c r="C4" t="str">
-        <v>Jack Lopez</v>
+        <v>Henry Rostova</v>
       </c>
       <c r="D4" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E4" t="str">
-        <v>KSBC-SAV-10050728</v>
+        <v>KSBC-SAV-10041776</v>
       </c>
       <c r="F4">
-        <v>4240000</v>
+        <v>1360000</v>
       </c>
       <c r="G4">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="H4">
         <v>60</v>
       </c>
       <c r="I4" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J4" t="str">
         <v>APPROVED</v>
       </c>
       <c r="K4">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="L4" t="str">
-        <v>HIGH</v>
+        <v>MODERATE</v>
       </c>
       <c r="M4" t="str">
-        <v>REJECT</v>
+        <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N4" t="str">
-        <v>Gemini Risk Score: 78/100 (HIGH) for Jack Lopez.</v>
+        <v>Gemini Risk Score: 42/100 (MODERATE) for Henry Rostova.</v>
       </c>
       <c r="O4" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4404,46 +4404,46 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>c0000028-1111-4111-c111-111111111111</v>
+        <v>c0000034-1111-4111-c111-111111111111</v>
       </c>
       <c r="B5" t="str">
-        <v>b0000028-1111-4111-b111-111111111111</v>
+        <v>b0000034-1111-4111-b111-111111111111</v>
       </c>
       <c r="C5" t="str">
-        <v>Henry Rostova</v>
+        <v>Jack Lopez</v>
       </c>
       <c r="D5" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E5" t="str">
-        <v>KSBC-SAV-10041776</v>
+        <v>KSBC-SAV-10050728</v>
       </c>
       <c r="F5">
-        <v>1360000</v>
+        <v>4240000</v>
       </c>
       <c r="G5">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
       <c r="H5">
         <v>60</v>
       </c>
       <c r="I5" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J5" t="str">
         <v>APPROVED</v>
       </c>
       <c r="K5">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="L5" t="str">
-        <v>MODERATE</v>
+        <v>HIGH</v>
       </c>
       <c r="M5" t="str">
-        <v>CONDITIONAL_APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N5" t="str">
-        <v>Gemini Risk Score: 42/100 (MODERATE) for Henry Rostova.</v>
+        <v>Gemini Risk Score: 78/100 (HIGH) for Jack Lopez.</v>
       </c>
       <c r="O5" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4460,31 +4460,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c0000004-1111-4111-c111-111111111111</v>
+        <v>c0000016-1111-4111-c111-111111111111</v>
       </c>
       <c r="B6" t="str">
-        <v>b0000004-1111-4111-b111-111111111111</v>
+        <v>b0000016-1111-4111-b111-111111111111</v>
       </c>
       <c r="C6" t="str">
-        <v>Elena Smith</v>
+        <v>Daniel Patel</v>
       </c>
       <c r="D6" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E6" t="str">
-        <v>KSBC-SAV-10005968</v>
+        <v>KSBC-SAV-10023872</v>
       </c>
       <c r="F6">
-        <v>1840000</v>
+        <v>7600000</v>
       </c>
       <c r="G6">
-        <v>6.75</v>
+        <v>9.75</v>
       </c>
       <c r="H6">
         <v>60</v>
       </c>
       <c r="I6" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J6" t="str">
         <v>APPROVED</v>
@@ -4499,7 +4499,7 @@
         <v>REJECT</v>
       </c>
       <c r="N6" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Daniel Patel.</v>
       </c>
       <c r="O6" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4516,31 +4516,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c0000016-1111-4111-c111-111111111111</v>
+        <v>c0000004-1111-4111-c111-111111111111</v>
       </c>
       <c r="B7" t="str">
-        <v>b0000016-1111-4111-b111-111111111111</v>
+        <v>b0000004-1111-4111-b111-111111111111</v>
       </c>
       <c r="C7" t="str">
-        <v>Daniel Patel</v>
+        <v>Elena Smith</v>
       </c>
       <c r="D7" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E7" t="str">
-        <v>KSBC-SAV-10023872</v>
+        <v>KSBC-SAV-10005968</v>
       </c>
       <c r="F7">
-        <v>7600000</v>
+        <v>1840000</v>
       </c>
       <c r="G7">
-        <v>9.75</v>
+        <v>6.75</v>
       </c>
       <c r="H7">
         <v>60</v>
       </c>
       <c r="I7" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J7" t="str">
         <v>APPROVED</v>
@@ -4555,7 +4555,7 @@
         <v>REJECT</v>
       </c>
       <c r="N7" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Daniel Patel.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
       </c>
       <c r="O7" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4695,31 +4695,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c0000049-1111-4111-c111-111111111111</v>
+        <v>c0000043-1111-4111-c111-111111111111</v>
       </c>
       <c r="B2" t="str">
-        <v>b0000049-1111-4111-b111-111111111111</v>
+        <v>b0000043-1111-4111-b111-111111111111</v>
       </c>
       <c r="C2" t="str">
-        <v>Ananya Taylor</v>
+        <v>David Reddy</v>
       </c>
       <c r="D2" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E2" t="str">
-        <v>KSBC-SAV-10073108</v>
+        <v>KSBC-SAV-10064156</v>
       </c>
       <c r="F2">
-        <v>11440000</v>
+        <v>8560000</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>12</v>
       </c>
       <c r="I2" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J2" t="str">
         <v>UNDERWRITING</v>
@@ -4751,46 +4751,46 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c0000043-1111-4111-c111-111111111111</v>
+        <v>c0000044-1111-4111-c111-111111111111</v>
       </c>
       <c r="B3" t="str">
-        <v>b0000043-1111-4111-b111-111111111111</v>
+        <v>b0000044-1111-4111-b111-111111111111</v>
       </c>
       <c r="C3" t="str">
-        <v>David Reddy</v>
+        <v>Elena Smith</v>
       </c>
       <c r="D3" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E3" t="str">
-        <v>KSBC-SAV-10064156</v>
+        <v>KSBC-SAV-10065648</v>
       </c>
       <c r="F3">
-        <v>8560000</v>
+        <v>9040000</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I3" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J3" t="str">
-        <v>UNDERWRITING</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K3">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="L3" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M3" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N3" t="str">
-        <v>Standard low-risk profile approved under baseline AI parameters.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
       </c>
       <c r="O3" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4807,46 +4807,46 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>c0000051-1111-4111-c111-111111111111</v>
+        <v>c0000050-1111-4111-c111-111111111111</v>
       </c>
       <c r="B4" t="str">
-        <v>b0000051-1111-4111-b111-111111111111</v>
+        <v>b0000050-1111-4111-b111-111111111111</v>
       </c>
       <c r="C4" t="str">
-        <v>Michael Thompson</v>
+        <v>Rohan Martin</v>
       </c>
       <c r="D4" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E4" t="str">
-        <v>KSBC-SAV-10076092</v>
+        <v>KSBC-SAV-10074600</v>
       </c>
       <c r="F4">
-        <v>400000</v>
+        <v>11920000</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="H4">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I4" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J4" t="str">
-        <v>UNDERWRITING</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K4">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L4" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M4" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N4" t="str">
-        <v>Gemini Risk Score: 24/100 (LOW) for Michael Thompson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rohan Martin.</v>
       </c>
       <c r="O4" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4863,34 +4863,34 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>c0000050-1111-4111-c111-111111111111</v>
+        <v>c0000045-1111-4111-c111-111111111111</v>
       </c>
       <c r="B5" t="str">
-        <v>b0000050-1111-4111-b111-111111111111</v>
+        <v>b0000045-1111-4111-b111-111111111111</v>
       </c>
       <c r="C5" t="str">
-        <v>Rohan Martin</v>
+        <v>Marcus Jones</v>
       </c>
       <c r="D5" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E5" t="str">
-        <v>KSBC-SAV-10074600</v>
+        <v>KSBC-SAV-10067140</v>
       </c>
       <c r="F5">
-        <v>11920000</v>
+        <v>9520000</v>
       </c>
       <c r="G5">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="H5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I5" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J5" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K5">
         <v>94</v>
@@ -4902,7 +4902,7 @@
         <v>REJECT</v>
       </c>
       <c r="N5" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rohan Martin.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
       </c>
       <c r="O5" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4919,46 +4919,46 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c0000045-1111-4111-c111-111111111111</v>
+        <v>c0000051-1111-4111-c111-111111111111</v>
       </c>
       <c r="B6" t="str">
-        <v>b0000045-1111-4111-b111-111111111111</v>
+        <v>b0000051-1111-4111-b111-111111111111</v>
       </c>
       <c r="C6" t="str">
-        <v>Marcus Jones</v>
+        <v>Michael Thompson</v>
       </c>
       <c r="D6" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E6" t="str">
-        <v>KSBC-SAV-10067140</v>
+        <v>KSBC-SAV-10076092</v>
       </c>
       <c r="F6">
-        <v>9520000</v>
+        <v>400000</v>
       </c>
       <c r="G6">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>36</v>
       </c>
       <c r="I6" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J6" t="str">
         <v>UNDERWRITING</v>
       </c>
       <c r="K6">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="L6" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M6" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N6" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Marcus Jones.</v>
+        <v>Gemini Risk Score: 24/100 (LOW) for Michael Thompson.</v>
       </c>
       <c r="O6" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -4975,46 +4975,46 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c0000044-1111-4111-c111-111111111111</v>
+        <v>c0000049-1111-4111-c111-111111111111</v>
       </c>
       <c r="B7" t="str">
-        <v>b0000044-1111-4111-b111-111111111111</v>
+        <v>b0000049-1111-4111-b111-111111111111</v>
       </c>
       <c r="C7" t="str">
-        <v>Elena Smith</v>
+        <v>Ananya Taylor</v>
       </c>
       <c r="D7" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E7" t="str">
-        <v>KSBC-SAV-10065648</v>
+        <v>KSBC-SAV-10073108</v>
       </c>
       <c r="F7">
-        <v>9040000</v>
+        <v>11440000</v>
       </c>
       <c r="G7">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I7" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J7" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K7">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L7" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M7" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N7" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Elena Smith.</v>
+        <v>Standard low-risk profile approved under baseline AI parameters.</v>
       </c>
       <c r="O7" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5087,46 +5087,46 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>c0000026-1111-4111-c111-111111111111</v>
+        <v>c0000032-1111-4111-c111-111111111111</v>
       </c>
       <c r="B9" t="str">
-        <v>b0000026-1111-4111-b111-111111111111</v>
+        <v>b0000032-1111-4111-b111-111111111111</v>
       </c>
       <c r="C9" t="str">
-        <v>Lucas Ramirez</v>
+        <v>Sebastian Garcia</v>
       </c>
       <c r="D9" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E9" t="str">
-        <v>KSBC-SAV-10038792</v>
+        <v>KSBC-SAV-10047744</v>
       </c>
       <c r="F9">
-        <v>400000</v>
+        <v>3280000</v>
       </c>
       <c r="G9">
-        <v>5.25</v>
+        <v>9.75</v>
       </c>
       <c r="H9">
         <v>24</v>
       </c>
       <c r="I9" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J9" t="str">
         <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K9">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="L9" t="str">
-        <v>LOW</v>
+        <v>MODERATE</v>
       </c>
       <c r="M9" t="str">
-        <v>APPROVE</v>
+        <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N9" t="str">
-        <v>Gemini Risk Score: 27/100 (LOW) for Lucas Ramirez.</v>
+        <v>Gemini Risk Score: 68/100 (MODERATE) for Sebastian Garcia.</v>
       </c>
       <c r="O9" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5143,46 +5143,46 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>c0000027-1111-4111-c111-111111111111</v>
+        <v>c0000033-1111-4111-c111-111111111111</v>
       </c>
       <c r="B10" t="str">
-        <v>b0000027-1111-4111-b111-111111111111</v>
+        <v>b0000033-1111-4111-b111-111111111111</v>
       </c>
       <c r="C10" t="str">
-        <v>Charlotte Sterling</v>
+        <v>Evelyn Rodriguez</v>
       </c>
       <c r="D10" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E10" t="str">
-        <v>KSBC-SAV-10040284</v>
+        <v>KSBC-SAV-10049236</v>
       </c>
       <c r="F10">
-        <v>880000</v>
+        <v>3760000</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H10">
         <v>36</v>
       </c>
       <c r="I10" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J10" t="str">
         <v>UNDERWRITING</v>
       </c>
       <c r="K10">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L10" t="str">
-        <v>LOW</v>
+        <v>HIGH</v>
       </c>
       <c r="M10" t="str">
-        <v>APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N10" t="str">
-        <v>Gemini Risk Score: 35/100 (LOW) for Charlotte Sterling.</v>
+        <v>Gemini Risk Score: 73/100 (HIGH) for Evelyn Rodriguez.</v>
       </c>
       <c r="O10" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5199,46 +5199,46 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>c0000032-1111-4111-c111-111111111111</v>
+        <v>c0000027-1111-4111-c111-111111111111</v>
       </c>
       <c r="B11" t="str">
-        <v>b0000032-1111-4111-b111-111111111111</v>
+        <v>b0000027-1111-4111-b111-111111111111</v>
       </c>
       <c r="C11" t="str">
-        <v>Sebastian Garcia</v>
+        <v>Charlotte Sterling</v>
       </c>
       <c r="D11" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E11" t="str">
-        <v>KSBC-SAV-10047744</v>
+        <v>KSBC-SAV-10040284</v>
       </c>
       <c r="F11">
-        <v>3280000</v>
+        <v>880000</v>
       </c>
       <c r="G11">
-        <v>9.75</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I11" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J11" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K11">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="L11" t="str">
-        <v>MODERATE</v>
+        <v>LOW</v>
       </c>
       <c r="M11" t="str">
-        <v>CONDITIONAL_APPROVE</v>
+        <v>APPROVE</v>
       </c>
       <c r="N11" t="str">
-        <v>Gemini Risk Score: 68/100 (MODERATE) for Sebastian Garcia.</v>
+        <v>Gemini Risk Score: 35/100 (LOW) for Charlotte Sterling.</v>
       </c>
       <c r="O11" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5255,37 +5255,37 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>c0000033-1111-4111-c111-111111111111</v>
+        <v>c0000038-1111-4111-c111-111111111111</v>
       </c>
       <c r="B12" t="str">
-        <v>b0000033-1111-4111-b111-111111111111</v>
+        <v>b0000038-1111-4111-b111-111111111111</v>
       </c>
       <c r="C12" t="str">
-        <v>Evelyn Rodriguez</v>
+        <v>Theodore White</v>
       </c>
       <c r="D12" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E12" t="str">
-        <v>KSBC-SAV-10049236</v>
+        <v>KSBC-SAV-10056696</v>
       </c>
       <c r="F12">
-        <v>3760000</v>
+        <v>6160000</v>
       </c>
       <c r="G12">
-        <v>4.5</v>
+        <v>8.25</v>
       </c>
       <c r="H12">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I12" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J12" t="str">
-        <v>UNDERWRITING</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K12">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L12" t="str">
         <v>HIGH</v>
@@ -5294,7 +5294,7 @@
         <v>REJECT</v>
       </c>
       <c r="N12" t="str">
-        <v>Gemini Risk Score: 73/100 (HIGH) for Evelyn Rodriguez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Theodore White.</v>
       </c>
       <c r="O12" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5311,34 +5311,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>c0000038-1111-4111-c111-111111111111</v>
+        <v>c0000039-1111-4111-c111-111111111111</v>
       </c>
       <c r="B13" t="str">
-        <v>b0000038-1111-4111-b111-111111111111</v>
+        <v>b0000039-1111-4111-b111-111111111111</v>
       </c>
       <c r="C13" t="str">
-        <v>Theodore White</v>
+        <v>Ella Clark</v>
       </c>
       <c r="D13" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E13" t="str">
-        <v>KSBC-SAV-10056696</v>
+        <v>KSBC-SAV-10058188</v>
       </c>
       <c r="F13">
-        <v>6160000</v>
+        <v>6640000</v>
       </c>
       <c r="G13">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I13" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J13" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K13">
         <v>94</v>
@@ -5350,7 +5350,7 @@
         <v>REJECT</v>
       </c>
       <c r="N13" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Theodore White.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Ella Clark.</v>
       </c>
       <c r="O13" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5367,46 +5367,46 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>c0000039-1111-4111-c111-111111111111</v>
+        <v>c0000026-1111-4111-c111-111111111111</v>
       </c>
       <c r="B14" t="str">
-        <v>b0000039-1111-4111-b111-111111111111</v>
+        <v>b0000026-1111-4111-b111-111111111111</v>
       </c>
       <c r="C14" t="str">
-        <v>Ella Clark</v>
+        <v>Lucas Ramirez</v>
       </c>
       <c r="D14" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E14" t="str">
-        <v>KSBC-SAV-10058188</v>
+        <v>KSBC-SAV-10038792</v>
       </c>
       <c r="F14">
-        <v>6640000</v>
+        <v>400000</v>
       </c>
       <c r="G14">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="H14">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I14" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J14" t="str">
-        <v>UNDERWRITING</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K14">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="L14" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M14" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N14" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ella Clark.</v>
+        <v>Gemini Risk Score: 27/100 (LOW) for Lucas Ramirez.</v>
       </c>
       <c r="O14" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5423,34 +5423,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>c0000015-1111-4111-c111-111111111111</v>
+        <v>c0000002-1111-4111-c111-111111111111</v>
       </c>
       <c r="B15" t="str">
-        <v>b0000015-1111-4111-b111-111111111111</v>
+        <v>b0000002-1111-4111-b111-111111111111</v>
       </c>
       <c r="C15" t="str">
-        <v>Amanda Vance</v>
+        <v>Sarah Green</v>
       </c>
       <c r="D15" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E15" t="str">
-        <v>KSBC-SAV-10022380</v>
+        <v>KSBC-SAV-10002984</v>
       </c>
       <c r="F15">
-        <v>7120000</v>
+        <v>880000</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="H15">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I15" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J15" t="str">
-        <v>UNDERWRITING</v>
+        <v>COMPLIANCE_REVIEW</v>
       </c>
       <c r="K15">
         <v>94</v>
@@ -5462,7 +5462,7 @@
         <v>REJECT</v>
       </c>
       <c r="N15" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Amanda Vance.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
       </c>
       <c r="O15" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5479,46 +5479,46 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>c0000020-1111-4111-c111-111111111111</v>
+        <v>c0000014-1111-4111-c111-111111111111</v>
       </c>
       <c r="B16" t="str">
-        <v>b0000020-1111-4111-b111-111111111111</v>
+        <v>b0000014-1111-4111-b111-111111111111</v>
       </c>
       <c r="C16" t="str">
-        <v>Ethan Martinez</v>
+        <v>Christopher Jenkins</v>
       </c>
       <c r="D16" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E16" t="str">
-        <v>KSBC-SAV-10029840</v>
+        <v>KSBC-SAV-10020888</v>
       </c>
       <c r="F16">
-        <v>9520000</v>
+        <v>6640000</v>
       </c>
       <c r="G16">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="H16">
         <v>24</v>
       </c>
       <c r="I16" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J16" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K16">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L16" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M16" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N16" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ethan Martinez.</v>
+        <v>Applicant David Reddy (Account: KSBC-SAV-10049281) evaluated under baseline AI underwriting parameters.</v>
       </c>
       <c r="O16" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5591,34 +5591,34 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>c0000002-1111-4111-c111-111111111111</v>
+        <v>c0000015-1111-4111-c111-111111111111</v>
       </c>
       <c r="B18" t="str">
-        <v>b0000002-1111-4111-b111-111111111111</v>
+        <v>b0000015-1111-4111-b111-111111111111</v>
       </c>
       <c r="C18" t="str">
-        <v>Sarah Green</v>
+        <v>Amanda Vance</v>
       </c>
       <c r="D18" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E18" t="str">
-        <v>KSBC-SAV-10002984</v>
+        <v>KSBC-SAV-10022380</v>
       </c>
       <c r="F18">
-        <v>880000</v>
+        <v>7120000</v>
       </c>
       <c r="G18">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="H18">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I18" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J18" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K18">
         <v>94</v>
@@ -5630,7 +5630,7 @@
         <v>REJECT</v>
       </c>
       <c r="N18" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Amanda Vance.</v>
       </c>
       <c r="O18" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5647,31 +5647,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>c0000014-1111-4111-c111-111111111111</v>
+        <v>c0000008-1111-4111-c111-111111111111</v>
       </c>
       <c r="B19" t="str">
-        <v>b0000014-1111-4111-b111-111111111111</v>
+        <v>b0000008-1111-4111-b111-111111111111</v>
       </c>
       <c r="C19" t="str">
-        <v>Christopher Jenkins</v>
+        <v>Priya Wilson</v>
       </c>
       <c r="D19" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E19" t="str">
-        <v>KSBC-SAV-10020888</v>
+        <v>KSBC-SAV-10011936</v>
       </c>
       <c r="F19">
-        <v>6640000</v>
+        <v>3760000</v>
       </c>
       <c r="G19">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="H19">
         <v>24</v>
       </c>
       <c r="I19" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J19" t="str">
         <v>COMPLIANCE_REVIEW</v>
@@ -5686,7 +5686,7 @@
         <v>REJECT</v>
       </c>
       <c r="N19" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Christopher Jenkins.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
       </c>
       <c r="O19" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5703,46 +5703,46 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>c0000009-1111-4111-c111-111111111111</v>
+        <v>c0000020-1111-4111-c111-111111111111</v>
       </c>
       <c r="B20" t="str">
-        <v>b0000009-1111-4111-b111-111111111111</v>
+        <v>b0000020-1111-4111-b111-111111111111</v>
       </c>
       <c r="C20" t="str">
-        <v>Ananya Taylor</v>
+        <v>Ethan Martinez</v>
       </c>
       <c r="D20" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E20" t="str">
-        <v>KSBC-SAV-10013428</v>
+        <v>KSBC-SAV-10029840</v>
       </c>
       <c r="F20">
-        <v>4240000</v>
+        <v>9520000</v>
       </c>
       <c r="G20">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="H20">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I20" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J20" t="str">
         <v>UNDERWRITING</v>
       </c>
       <c r="K20">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="L20" t="str">
-        <v>HIGH</v>
+        <v>LOW</v>
       </c>
       <c r="M20" t="str">
-        <v>REJECT</v>
+        <v>APPROVE</v>
       </c>
       <c r="N20" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Ananya Taylor.</v>
+        <v>Applicant David Reddy (Account: KSBC-SAV-10049281) evaluated under baseline AI underwriting parameters.</v>
       </c>
       <c r="O20" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5759,34 +5759,34 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>c0000008-1111-4111-c111-111111111111</v>
+        <v>c0000009-1111-4111-c111-111111111111</v>
       </c>
       <c r="B21" t="str">
-        <v>b0000008-1111-4111-b111-111111111111</v>
+        <v>b0000009-1111-4111-b111-111111111111</v>
       </c>
       <c r="C21" t="str">
-        <v>Priya Wilson</v>
+        <v>Ananya Taylor</v>
       </c>
       <c r="D21" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E21" t="str">
-        <v>KSBC-SAV-10011936</v>
+        <v>KSBC-SAV-10013428</v>
       </c>
       <c r="F21">
-        <v>3760000</v>
+        <v>4240000</v>
       </c>
       <c r="G21">
-        <v>9.75</v>
+        <v>4.5</v>
       </c>
       <c r="H21">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I21" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J21" t="str">
-        <v>COMPLIANCE_REVIEW</v>
+        <v>UNDERWRITING</v>
       </c>
       <c r="K21">
         <v>94</v>
@@ -5798,7 +5798,7 @@
         <v>REJECT</v>
       </c>
       <c r="N21" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Ananya Taylor.</v>
       </c>
       <c r="O21" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5882,46 +5882,46 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>c0000025-1111-4111-c111-111111111111</v>
+        <v>c0000031-1111-4111-c111-111111111111</v>
       </c>
       <c r="B2" t="str">
-        <v>b0000025-1111-4111-b111-111111111111</v>
+        <v>b0000031-1111-4111-b111-111111111111</v>
       </c>
       <c r="C2" t="str">
-        <v>Mia Harris</v>
+        <v>Harper Williams</v>
       </c>
       <c r="D2" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E2" t="str">
-        <v>KSBC-SAV-10037300</v>
+        <v>KSBC-SAV-10046252</v>
       </c>
       <c r="F2">
-        <v>11920000</v>
+        <v>2800000</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>12</v>
       </c>
       <c r="I2" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>Commercial Real Estate Acquisition</v>
       </c>
       <c r="J2" t="str">
         <v>DRAFT</v>
       </c>
       <c r="K2">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="L2" t="str">
-        <v>HIGH</v>
+        <v>MODERATE</v>
       </c>
       <c r="M2" t="str">
-        <v>REJECT</v>
+        <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N2" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Mia Harris.</v>
+        <v>Gemini Risk Score: 62/100 (MODERATE) for Harper Williams.</v>
       </c>
       <c r="O2" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -5938,46 +5938,46 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c0000031-1111-4111-c111-111111111111</v>
+        <v>c0000025-1111-4111-c111-111111111111</v>
       </c>
       <c r="B3" t="str">
-        <v>b0000031-1111-4111-b111-111111111111</v>
+        <v>b0000025-1111-4111-b111-111111111111</v>
       </c>
       <c r="C3" t="str">
-        <v>Harper Williams</v>
+        <v>Mia Harris</v>
       </c>
       <c r="D3" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E3" t="str">
-        <v>KSBC-SAV-10046252</v>
+        <v>KSBC-SAV-10037300</v>
       </c>
       <c r="F3">
-        <v>2800000</v>
+        <v>11920000</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
       <c r="I3" t="str">
-        <v>Commercial Real Estate Acquisition</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J3" t="str">
         <v>DRAFT</v>
       </c>
       <c r="K3">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="L3" t="str">
-        <v>MODERATE</v>
+        <v>HIGH</v>
       </c>
       <c r="M3" t="str">
-        <v>CONDITIONAL_APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N3" t="str">
-        <v>Gemini Risk Score: 62/100 (MODERATE) for Harper Williams.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Mia Harris.</v>
       </c>
       <c r="O3" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6050,31 +6050,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>c0000019-1111-4111-c111-111111111111</v>
+        <v>c0000001-1111-4111-c111-111111111111</v>
       </c>
       <c r="B5" t="str">
-        <v>b0000019-1111-4111-b111-111111111111</v>
+        <v>b0000001-1111-4111-b111-111111111111</v>
       </c>
       <c r="C5" t="str">
-        <v>Olivia Miller</v>
+        <v>Alexander Chen</v>
       </c>
       <c r="D5" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E5" t="str">
-        <v>KSBC-SAV-10028348</v>
+        <v>KSBC-SAV-10001492</v>
       </c>
       <c r="F5">
-        <v>9040000</v>
+        <v>400000</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="H5">
         <v>12</v>
       </c>
       <c r="I5" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J5" t="str">
         <v>DRAFT</v>
@@ -6089,7 +6089,7 @@
         <v>REJECT</v>
       </c>
       <c r="N5" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Olivia Miller.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
       </c>
       <c r="O5" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6106,31 +6106,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c0000001-1111-4111-c111-111111111111</v>
+        <v>c0000019-1111-4111-c111-111111111111</v>
       </c>
       <c r="B6" t="str">
-        <v>b0000001-1111-4111-b111-111111111111</v>
+        <v>b0000019-1111-4111-b111-111111111111</v>
       </c>
       <c r="C6" t="str">
-        <v>Alexander Chen</v>
+        <v>Olivia Miller</v>
       </c>
       <c r="D6" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E6" t="str">
-        <v>KSBC-SAV-10001492</v>
+        <v>KSBC-SAV-10028348</v>
       </c>
       <c r="F6">
-        <v>400000</v>
+        <v>9040000</v>
       </c>
       <c r="G6">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
       <c r="I6" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J6" t="str">
         <v>DRAFT</v>
@@ -6145,7 +6145,7 @@
         <v>REJECT</v>
       </c>
       <c r="N6" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Alexander Chen.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Olivia Miller.</v>
       </c>
       <c r="O6" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6162,31 +6162,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c0000013-1111-4111-c111-111111111111</v>
+        <v>c0000007-1111-4111-c111-111111111111</v>
       </c>
       <c r="B7" t="str">
-        <v>b0000013-1111-4111-b111-111111111111</v>
+        <v>b0000007-1111-4111-b111-111111111111</v>
       </c>
       <c r="C7" t="str">
-        <v>Emily Lewis</v>
+        <v>Vikram Hernandez</v>
       </c>
       <c r="D7" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E7" t="str">
-        <v>KSBC-SAV-10019396</v>
+        <v>KSBC-SAV-10010444</v>
       </c>
       <c r="F7">
-        <v>6160000</v>
+        <v>3280000</v>
       </c>
       <c r="G7">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>12</v>
       </c>
       <c r="I7" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J7" t="str">
         <v>DRAFT</v>
@@ -6201,7 +6201,7 @@
         <v>REJECT</v>
       </c>
       <c r="N7" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Emily Lewis.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Vikram Hernandez.</v>
       </c>
       <c r="O7" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6218,31 +6218,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>c0000007-1111-4111-c111-111111111111</v>
+        <v>c0000013-1111-4111-c111-111111111111</v>
       </c>
       <c r="B8" t="str">
-        <v>b0000007-1111-4111-b111-111111111111</v>
+        <v>b0000013-1111-4111-b111-111111111111</v>
       </c>
       <c r="C8" t="str">
-        <v>Vikram Hernandez</v>
+        <v>Emily Lewis</v>
       </c>
       <c r="D8" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E8" t="str">
-        <v>KSBC-SAV-10010444</v>
+        <v>KSBC-SAV-10019396</v>
       </c>
       <c r="F8">
-        <v>3280000</v>
+        <v>6160000</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H8">
         <v>12</v>
       </c>
       <c r="I8" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J8" t="str">
         <v>DRAFT</v>
@@ -6257,7 +6257,7 @@
         <v>REJECT</v>
       </c>
       <c r="N8" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Vikram Hernandez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Emily Lewis.</v>
       </c>
       <c r="O8" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6397,31 +6397,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>c0000048-1111-4111-c111-111111111111</v>
+        <v>c0000042-1111-4111-c111-111111111111</v>
       </c>
       <c r="B3" t="str">
-        <v>b0000048-1111-4111-b111-111111111111</v>
+        <v>b0000042-1111-4111-b111-111111111111</v>
       </c>
       <c r="C3" t="str">
-        <v>Priya Wilson</v>
+        <v>Sarah Green</v>
       </c>
       <c r="D3" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E3" t="str">
-        <v>KSBC-SAV-10071616</v>
+        <v>KSBC-SAV-10062664</v>
       </c>
       <c r="F3">
-        <v>10960000</v>
+        <v>8080000</v>
       </c>
       <c r="G3">
-        <v>9.75</v>
+        <v>5.25</v>
       </c>
       <c r="H3">
         <v>240</v>
       </c>
       <c r="I3" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Estate Development &amp; High Net-Worth Credit</v>
       </c>
       <c r="J3" t="str">
         <v>REJECTED</v>
@@ -6436,7 +6436,7 @@
         <v>REJECT</v>
       </c>
       <c r="N3" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
       </c>
       <c r="O3" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6453,31 +6453,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>c0000042-1111-4111-c111-111111111111</v>
+        <v>c0000048-1111-4111-c111-111111111111</v>
       </c>
       <c r="B4" t="str">
-        <v>b0000042-1111-4111-b111-111111111111</v>
+        <v>b0000048-1111-4111-b111-111111111111</v>
       </c>
       <c r="C4" t="str">
-        <v>Sarah Green</v>
+        <v>Priya Wilson</v>
       </c>
       <c r="D4" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E4" t="str">
-        <v>KSBC-SAV-10062664</v>
+        <v>KSBC-SAV-10071616</v>
       </c>
       <c r="F4">
-        <v>8080000</v>
+        <v>10960000</v>
       </c>
       <c r="G4">
-        <v>5.25</v>
+        <v>9.75</v>
       </c>
       <c r="H4">
         <v>240</v>
       </c>
       <c r="I4" t="str">
-        <v>Estate Development &amp; High Net-Worth Credit</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J4" t="str">
         <v>REJECTED</v>
@@ -6492,7 +6492,7 @@
         <v>REJECT</v>
       </c>
       <c r="N4" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Sarah Green.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Priya Wilson.</v>
       </c>
       <c r="O4" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6565,46 +6565,46 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c0000030-1111-4111-c111-111111111111</v>
+        <v>c0000036-1111-4111-c111-111111111111</v>
       </c>
       <c r="B6" t="str">
-        <v>b0000030-1111-4111-b111-111111111111</v>
+        <v>b0000036-1111-4111-b111-111111111111</v>
       </c>
       <c r="C6" t="str">
-        <v>Alexander Mehta</v>
+        <v>Owen Moore</v>
       </c>
       <c r="D6" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E6" t="str">
-        <v>KSBC-SAV-10044760</v>
+        <v>KSBC-SAV-10053712</v>
       </c>
       <c r="F6">
-        <v>2320000</v>
+        <v>5200000</v>
       </c>
       <c r="G6">
-        <v>8.25</v>
+        <v>6.75</v>
       </c>
       <c r="H6">
         <v>240</v>
       </c>
       <c r="I6" t="str">
-        <v>Working Capital Expansion</v>
+        <v>Equipment Purchase &amp; Automation</v>
       </c>
       <c r="J6" t="str">
         <v>REJECTED</v>
       </c>
       <c r="K6">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="L6" t="str">
-        <v>MODERATE</v>
+        <v>HIGH</v>
       </c>
       <c r="M6" t="str">
-        <v>CONDITIONAL_APPROVE</v>
+        <v>REJECT</v>
       </c>
       <c r="N6" t="str">
-        <v>Gemini Risk Score: 56/100 (MODERATE) for Alexander Mehta.</v>
+        <v>Gemini Risk Score: 87/100 (HIGH) for Owen Moore.</v>
       </c>
       <c r="O6" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6621,46 +6621,46 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>c0000036-1111-4111-c111-111111111111</v>
+        <v>c0000030-1111-4111-c111-111111111111</v>
       </c>
       <c r="B7" t="str">
-        <v>b0000036-1111-4111-b111-111111111111</v>
+        <v>b0000030-1111-4111-b111-111111111111</v>
       </c>
       <c r="C7" t="str">
-        <v>Owen Moore</v>
+        <v>Alexander Mehta</v>
       </c>
       <c r="D7" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E7" t="str">
-        <v>KSBC-SAV-10053712</v>
+        <v>KSBC-SAV-10044760</v>
       </c>
       <c r="F7">
-        <v>5200000</v>
+        <v>2320000</v>
       </c>
       <c r="G7">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="H7">
         <v>240</v>
       </c>
       <c r="I7" t="str">
-        <v>Equipment Purchase &amp; Automation</v>
+        <v>Working Capital Expansion</v>
       </c>
       <c r="J7" t="str">
         <v>REJECTED</v>
       </c>
       <c r="K7">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="L7" t="str">
-        <v>HIGH</v>
+        <v>MODERATE</v>
       </c>
       <c r="M7" t="str">
-        <v>REJECT</v>
+        <v>CONDITIONAL_APPROVE</v>
       </c>
       <c r="N7" t="str">
-        <v>Gemini Risk Score: 87/100 (HIGH) for Owen Moore.</v>
+        <v>Gemini Risk Score: 56/100 (MODERATE) for Alexander Mehta.</v>
       </c>
       <c r="O7" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6677,31 +6677,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>c0000006-1111-4111-c111-111111111111</v>
+        <v>c0000018-1111-4111-c111-111111111111</v>
       </c>
       <c r="B8" t="str">
-        <v>b0000006-1111-4111-b111-111111111111</v>
+        <v>b0000018-1111-4111-b111-111111111111</v>
       </c>
       <c r="C8" t="str">
-        <v>Rachel Davis</v>
+        <v>James Brown</v>
       </c>
       <c r="D8" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E8" t="str">
-        <v>KSBC-SAV-10008952</v>
+        <v>KSBC-SAV-10026856</v>
       </c>
       <c r="F8">
-        <v>2800000</v>
+        <v>8560000</v>
       </c>
       <c r="G8">
-        <v>8.25</v>
+        <v>5.25</v>
       </c>
       <c r="H8">
         <v>240</v>
       </c>
       <c r="I8" t="str">
-        <v>Personal Wealth Portfolio Scaling</v>
+        <v>Debt Refinancing &amp; Consolidation</v>
       </c>
       <c r="J8" t="str">
         <v>REJECTED</v>
@@ -6716,7 +6716,7 @@
         <v>REJECT</v>
       </c>
       <c r="N8" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for James Brown.</v>
       </c>
       <c r="O8" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6733,31 +6733,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>c0000018-1111-4111-c111-111111111111</v>
+        <v>c0000012-1111-4111-c111-111111111111</v>
       </c>
       <c r="B9" t="str">
-        <v>b0000018-1111-4111-b111-111111111111</v>
+        <v>b0000012-1111-4111-b111-111111111111</v>
       </c>
       <c r="C9" t="str">
-        <v>James Brown</v>
+        <v>Jessica Sanchez</v>
       </c>
       <c r="D9" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E9" t="str">
-        <v>KSBC-SAV-10026856</v>
+        <v>KSBC-SAV-10017904</v>
       </c>
       <c r="F9">
-        <v>8560000</v>
+        <v>5680000</v>
       </c>
       <c r="G9">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="H9">
         <v>240</v>
       </c>
       <c r="I9" t="str">
-        <v>Debt Refinancing &amp; Consolidation</v>
+        <v>R&amp;D Facility Upgrade</v>
       </c>
       <c r="J9" t="str">
         <v>REJECTED</v>
@@ -6772,7 +6772,7 @@
         <v>REJECT</v>
       </c>
       <c r="N9" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for James Brown.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Jessica Sanchez.</v>
       </c>
       <c r="O9" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
@@ -6789,31 +6789,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>c0000012-1111-4111-c111-111111111111</v>
+        <v>c0000006-1111-4111-c111-111111111111</v>
       </c>
       <c r="B10" t="str">
-        <v>b0000012-1111-4111-b111-111111111111</v>
+        <v>b0000006-1111-4111-b111-111111111111</v>
       </c>
       <c r="C10" t="str">
-        <v>Jessica Sanchez</v>
+        <v>Rachel Davis</v>
       </c>
       <c r="D10" t="str">
         <v>PRIVATE SAVINGS</v>
       </c>
       <c r="E10" t="str">
-        <v>KSBC-SAV-10017904</v>
+        <v>KSBC-SAV-10008952</v>
       </c>
       <c r="F10">
-        <v>5680000</v>
+        <v>2800000</v>
       </c>
       <c r="G10">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="H10">
         <v>240</v>
       </c>
       <c r="I10" t="str">
-        <v>R&amp;D Facility Upgrade</v>
+        <v>Personal Wealth Portfolio Scaling</v>
       </c>
       <c r="J10" t="str">
         <v>REJECTED</v>
@@ -6828,7 +6828,7 @@
         <v>REJECT</v>
       </c>
       <c r="N10" t="str">
-        <v>Gemini Risk Score: 94/100 (HIGH) for Jessica Sanchez.</v>
+        <v>Gemini Risk Score: 94/100 (HIGH) for Rachel Davis.</v>
       </c>
       <c r="O10" t="str">
         <v>a2222222-2222-4222-a222-222222222222</v>
